--- a/Configs/GameConfig/Datas/fg/#MechEnemy-机械敌人.xlsx
+++ b/Configs/GameConfig/Datas/fg/#MechEnemy-机械敌人.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F9"/>
+  <dimension ref="A1:AM10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -447,6 +447,171 @@
           <t>scrapLoot</t>
         </is>
       </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>faction</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>role</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>tier</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>behavior</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>tags</t>
+        </is>
+      </c>
+      <c r="L1" t="inlineStr">
+        <is>
+          <t>speed</t>
+        </is>
+      </c>
+      <c r="M1" t="inlineStr">
+        <is>
+          <t>radius</t>
+        </is>
+      </c>
+      <c r="N1" t="inlineStr">
+        <is>
+          <t>weaponRange</t>
+        </is>
+      </c>
+      <c r="O1" t="inlineStr">
+        <is>
+          <t>weaponDamage</t>
+        </is>
+      </c>
+      <c r="P1" t="inlineStr">
+        <is>
+          <t>weaponCooldown</t>
+        </is>
+      </c>
+      <c r="Q1" t="inlineStr">
+        <is>
+          <t>weaponAim</t>
+        </is>
+      </c>
+      <c r="R1" t="inlineStr">
+        <is>
+          <t>senseRange</t>
+        </is>
+      </c>
+      <c r="S1" t="inlineStr">
+        <is>
+          <t>cycleSeconds</t>
+        </is>
+      </c>
+      <c r="T1" t="inlineStr">
+        <is>
+          <t>effectSeconds</t>
+        </is>
+      </c>
+      <c r="U1" t="inlineStr">
+        <is>
+          <t>effectRange</t>
+        </is>
+      </c>
+      <c r="V1" t="inlineStr">
+        <is>
+          <t>effectAmount</t>
+        </is>
+      </c>
+      <c r="W1" t="inlineStr">
+        <is>
+          <t>fleeTrigger</t>
+        </is>
+      </c>
+      <c r="X1" t="inlineStr">
+        <is>
+          <t>leash</t>
+        </is>
+      </c>
+      <c r="Y1" t="inlineStr">
+        <is>
+          <t>patrolRadius</t>
+        </is>
+      </c>
+      <c r="Z1" t="inlineStr">
+        <is>
+          <t>patrolFreq</t>
+        </is>
+      </c>
+      <c r="AA1" t="inlineStr">
+        <is>
+          <t>frontalHalfAngleDeg</t>
+        </is>
+      </c>
+      <c r="AB1" t="inlineStr">
+        <is>
+          <t>descKey</t>
+        </is>
+      </c>
+      <c r="AC1" t="inlineStr">
+        <is>
+          <t>weaknessKey</t>
+        </is>
+      </c>
+      <c r="AD1" t="inlineStr">
+        <is>
+          <t>traitKey</t>
+        </is>
+      </c>
+      <c r="AE1" t="inlineStr">
+        <is>
+          <t>components</t>
+        </is>
+      </c>
+      <c r="AF1" t="inlineStr">
+        <is>
+          <t>lootSource</t>
+        </is>
+      </c>
+      <c r="AG1" t="inlineStr">
+        <is>
+          <t>keyDrop</t>
+        </is>
+      </c>
+      <c r="AH1" t="inlineStr">
+        <is>
+          <t>raidPoints</t>
+        </is>
+      </c>
+      <c r="AI1" t="inlineStr">
+        <is>
+          <t>iconId</t>
+        </is>
+      </c>
+      <c r="AJ1" t="inlineStr">
+        <is>
+          <t>silhouette</t>
+        </is>
+      </c>
+      <c r="AK1" t="inlineStr">
+        <is>
+          <t>viewColor</t>
+        </is>
+      </c>
+      <c r="AL1" t="inlineStr">
+        <is>
+          <t>sfxId</t>
+        </is>
+      </c>
+      <c r="AM1" t="inlineStr">
+        <is>
+          <t>vfxId</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -479,6 +644,171 @@
           <t>int</t>
         </is>
       </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>float</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>float</t>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>float</t>
+        </is>
+      </c>
+      <c r="O2" t="inlineStr">
+        <is>
+          <t>float</t>
+        </is>
+      </c>
+      <c r="P2" t="inlineStr">
+        <is>
+          <t>float</t>
+        </is>
+      </c>
+      <c r="Q2" t="inlineStr">
+        <is>
+          <t>float</t>
+        </is>
+      </c>
+      <c r="R2" t="inlineStr">
+        <is>
+          <t>float</t>
+        </is>
+      </c>
+      <c r="S2" t="inlineStr">
+        <is>
+          <t>float</t>
+        </is>
+      </c>
+      <c r="T2" t="inlineStr">
+        <is>
+          <t>float</t>
+        </is>
+      </c>
+      <c r="U2" t="inlineStr">
+        <is>
+          <t>float</t>
+        </is>
+      </c>
+      <c r="V2" t="inlineStr">
+        <is>
+          <t>float</t>
+        </is>
+      </c>
+      <c r="W2" t="inlineStr">
+        <is>
+          <t>float</t>
+        </is>
+      </c>
+      <c r="X2" t="inlineStr">
+        <is>
+          <t>float</t>
+        </is>
+      </c>
+      <c r="Y2" t="inlineStr">
+        <is>
+          <t>float</t>
+        </is>
+      </c>
+      <c r="Z2" t="inlineStr">
+        <is>
+          <t>float</t>
+        </is>
+      </c>
+      <c r="AA2" t="inlineStr">
+        <is>
+          <t>float</t>
+        </is>
+      </c>
+      <c r="AB2" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="AD2" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="AE2" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="AF2" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="AG2" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="AH2" t="inlineStr">
+        <is>
+          <t>int</t>
+        </is>
+      </c>
+      <c r="AI2" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="AJ2" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="AK2" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="AL2" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="AM2" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -498,7 +828,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>最大生命</t>
+          <t>最大生命(耐久)</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -509,6 +839,171 @@
       <c r="F3" t="inlineStr">
         <is>
           <t>击破掉落废料,0=不走普通废料掉落</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>阵营:silent/foundry/clarity/overclock/fleet</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>职能(头顶图标/情报):scout/jammer/artillery/armor/support/boss/structure</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>层级:normal/elite/boss(elite 生成时带内核精英标记;boss 先于其它敌人结算)</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>行为读法(EnemyBehaviorReadings):none/patrol_mark/jam_field/hold_fire/telegraph/repair</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>标签(逗号分隔):structure/external_health/silent_fire/adapt_heat;none=没有</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>移动速度(米/秒),0=不移动</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>碰撞半径(米)</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>武器射程(米),0=没有武器</t>
+        </is>
+      </c>
+      <c r="O3" t="inlineStr">
+        <is>
+          <t>武器每发伤害(难度倍率另乘),没有武器写0</t>
+        </is>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>武器冷却(秒),没有武器写0</t>
+        </is>
+      </c>
+      <c r="Q3" t="inlineStr">
+        <is>
+          <t>瞄准线秒数(telegraph 两段式),0=即时</t>
+        </is>
+      </c>
+      <c r="R3" t="inlineStr">
+        <is>
+          <t>感知/标记距离(米),0=不感知</t>
+        </is>
+      </c>
+      <c r="S3" t="inlineStr">
+        <is>
+          <t>周期(秒):标记间隔/治疗间隔,0=没有周期</t>
+        </is>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>效果持续(秒):标记时长,0=没有</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>效果半径(米):干扰场半径/治疗距离,0=没有</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>效果量:每次治疗量,0=没有</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>受威胁后撤的触发距离(米),0=不后撤</t>
+        </is>
+      </c>
+      <c r="X3" t="inlineStr">
+        <is>
+          <t>牵引半径(米,后撤/巡逻不超出牵引中心这个距离),0=不移动</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>无威胁时的巡逻摆动半径(米),0=不巡逻</t>
+        </is>
+      </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>巡逻摆动频率,0=不巡逻</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>正面锥半角(度):正面减伤/侧后加成的判定</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t>图鉴描述文本键</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>图鉴弱点(应对)文本键</t>
+        </is>
+      </c>
+      <c r="AD3" t="inlineStr">
+        <is>
+          <t>出征情报特征文本键({0}=周期秒,{1}=效果半径,{2}=正面减伤%,{3}=瞄准秒,{4}=治疗量);none=只写名称与耐久</t>
+        </is>
+      </c>
+      <c r="AE3" t="inlineStr">
+        <is>
+          <t>敌方组件与固件(fg.TbCombatComponent.id / fg.TbFirmwareKind.id,逗号分隔);none=只用内置武器(Demo 敌人)</t>
+        </is>
+      </c>
+      <c r="AF3" t="inlineStr">
+        <is>
+          <t>掉落倾向(fg.TbLootDrop.source):minion/elite;none=不掷野外普通掉落(首领奖励另算)</t>
+        </is>
+      </c>
+      <c r="AG3" t="inlineStr">
+        <is>
+          <t>首次击破掉落的关键物 contentId;none=没有</t>
+        </is>
+      </c>
+      <c r="AH3" t="inlineStr">
+        <is>
+          <t>突袭点数(fg.TbRaidUnit.points 由此派生),0=不进突袭编成</t>
+        </is>
+      </c>
+      <c r="AI3" t="inlineStr">
+        <is>
+          <t>头顶标记/图鉴图标ID(GameRes/Raw/UI/Icons)</t>
+        </is>
+      </c>
+      <c r="AJ3" t="inlineStr">
+        <is>
+          <t>占位剪影(PlaceholderSilhouette):silent_orb/silent_ring/foundry_strider/foundry_shield/foundry_cross/foundry_block/foundry_node/foundry_reactor</t>
+        </is>
+      </c>
+      <c r="AK3" t="inlineStr">
+        <is>
+          <t>占位颜色(#RRGGBB)</t>
+        </is>
+      </c>
+      <c r="AL3" t="inlineStr">
+        <is>
+          <t>开火/行为音效ID</t>
+        </is>
+      </c>
+      <c r="AM3" t="inlineStr">
+        <is>
+          <t>行为特效ID(占位)</t>
         </is>
       </c>
     </row>
@@ -533,6 +1028,137 @@
       <c r="F4" t="n">
         <v>15</v>
       </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>silent</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>scout</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>patrol_mark</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="L4" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="M4" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="N4" t="n">
+        <v>0</v>
+      </c>
+      <c r="O4" t="n">
+        <v>0</v>
+      </c>
+      <c r="P4" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q4" t="n">
+        <v>0</v>
+      </c>
+      <c r="R4" t="n">
+        <v>10</v>
+      </c>
+      <c r="S4" t="n">
+        <v>8</v>
+      </c>
+      <c r="T4" t="n">
+        <v>10</v>
+      </c>
+      <c r="U4" t="n">
+        <v>0</v>
+      </c>
+      <c r="V4" t="n">
+        <v>0</v>
+      </c>
+      <c r="W4" t="n">
+        <v>6</v>
+      </c>
+      <c r="X4" t="n">
+        <v>5</v>
+      </c>
+      <c r="Y4" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="Z4" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="AA4" t="n">
+        <v>90</v>
+      </c>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>enemy.scout.desc</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>enemy.scout.weakness</t>
+        </is>
+      </c>
+      <c r="AD4" t="inlineStr">
+        <is>
+          <t>enemy.scout.trait</t>
+        </is>
+      </c>
+      <c r="AE4" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="AF4" t="inlineStr">
+        <is>
+          <t>minion</t>
+        </is>
+      </c>
+      <c r="AG4" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="AH4" t="n">
+        <v>10</v>
+      </c>
+      <c r="AI4" t="inlineStr">
+        <is>
+          <t>icon_enemy_scout</t>
+        </is>
+      </c>
+      <c r="AJ4" t="inlineStr">
+        <is>
+          <t>silent_orb</t>
+        </is>
+      </c>
+      <c r="AK4" t="inlineStr">
+        <is>
+          <t>#BF5926</t>
+        </is>
+      </c>
+      <c r="AL4" t="inlineStr">
+        <is>
+          <t>sfx_enemy_fire</t>
+        </is>
+      </c>
+      <c r="AM4" t="inlineStr">
+        <is>
+          <t>vfx_none_placeholder</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr"/>
@@ -555,6 +1181,137 @@
       <c r="F5" t="n">
         <v>20</v>
       </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>silent</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>jammer</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>jam_field</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="L5" t="n">
+        <v>0</v>
+      </c>
+      <c r="M5" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="N5" t="n">
+        <v>8</v>
+      </c>
+      <c r="O5" t="n">
+        <v>6</v>
+      </c>
+      <c r="P5" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>0</v>
+      </c>
+      <c r="R5" t="n">
+        <v>0</v>
+      </c>
+      <c r="S5" t="n">
+        <v>0</v>
+      </c>
+      <c r="T5" t="n">
+        <v>0</v>
+      </c>
+      <c r="U5" t="n">
+        <v>12</v>
+      </c>
+      <c r="V5" t="n">
+        <v>0</v>
+      </c>
+      <c r="W5" t="n">
+        <v>0</v>
+      </c>
+      <c r="X5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA5" t="n">
+        <v>90</v>
+      </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>enemy.jammer.desc</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>enemy.jammer.weakness</t>
+        </is>
+      </c>
+      <c r="AD5" t="inlineStr">
+        <is>
+          <t>enemy.jammer.trait</t>
+        </is>
+      </c>
+      <c r="AE5" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="AF5" t="inlineStr">
+        <is>
+          <t>minion</t>
+        </is>
+      </c>
+      <c r="AG5" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="AH5" t="n">
+        <v>18</v>
+      </c>
+      <c r="AI5" t="inlineStr">
+        <is>
+          <t>icon_enemy_jammer</t>
+        </is>
+      </c>
+      <c r="AJ5" t="inlineStr">
+        <is>
+          <t>silent_ring</t>
+        </is>
+      </c>
+      <c r="AK5" t="inlineStr">
+        <is>
+          <t>#99268C</t>
+        </is>
+      </c>
+      <c r="AL5" t="inlineStr">
+        <is>
+          <t>sfx_signal_jam</t>
+        </is>
+      </c>
+      <c r="AM5" t="inlineStr">
+        <is>
+          <t>vfx_jam_field_placeholder</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr"/>
@@ -577,6 +1334,137 @@
       <c r="F6" t="n">
         <v>30</v>
       </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>foundry</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>artillery</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>telegraph</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="L6" t="n">
+        <v>0</v>
+      </c>
+      <c r="M6" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="N6" t="n">
+        <v>14</v>
+      </c>
+      <c r="O6" t="n">
+        <v>20</v>
+      </c>
+      <c r="P6" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>1</v>
+      </c>
+      <c r="R6" t="n">
+        <v>0</v>
+      </c>
+      <c r="S6" t="n">
+        <v>0</v>
+      </c>
+      <c r="T6" t="n">
+        <v>0</v>
+      </c>
+      <c r="U6" t="n">
+        <v>0</v>
+      </c>
+      <c r="V6" t="n">
+        <v>0</v>
+      </c>
+      <c r="W6" t="n">
+        <v>0</v>
+      </c>
+      <c r="X6" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y6" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA6" t="n">
+        <v>90</v>
+      </c>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t>enemy.strider.desc</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>enemy.strider.weakness</t>
+        </is>
+      </c>
+      <c r="AD6" t="inlineStr">
+        <is>
+          <t>enemy.strider.trait</t>
+        </is>
+      </c>
+      <c r="AE6" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="AF6" t="inlineStr">
+        <is>
+          <t>minion</t>
+        </is>
+      </c>
+      <c r="AG6" t="inlineStr">
+        <is>
+          <t>quest_cannon_module</t>
+        </is>
+      </c>
+      <c r="AH6" t="n">
+        <v>22</v>
+      </c>
+      <c r="AI6" t="inlineStr">
+        <is>
+          <t>icon_enemy_strider</t>
+        </is>
+      </c>
+      <c r="AJ6" t="inlineStr">
+        <is>
+          <t>foundry_strider</t>
+        </is>
+      </c>
+      <c r="AK6" t="inlineStr">
+        <is>
+          <t>#B3401A</t>
+        </is>
+      </c>
+      <c r="AL6" t="inlineStr">
+        <is>
+          <t>sfx_enemy_cannon</t>
+        </is>
+      </c>
+      <c r="AM6" t="inlineStr">
+        <is>
+          <t>vfx_aim_line_placeholder</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr"/>
@@ -599,6 +1487,137 @@
       <c r="F7" t="n">
         <v>25</v>
       </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>foundry</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>armor</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>hold_fire</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>adapt_heat</t>
+        </is>
+      </c>
+      <c r="L7" t="n">
+        <v>0</v>
+      </c>
+      <c r="M7" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="N7" t="n">
+        <v>9</v>
+      </c>
+      <c r="O7" t="n">
+        <v>10</v>
+      </c>
+      <c r="P7" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>0</v>
+      </c>
+      <c r="R7" t="n">
+        <v>0</v>
+      </c>
+      <c r="S7" t="n">
+        <v>0</v>
+      </c>
+      <c r="T7" t="n">
+        <v>0</v>
+      </c>
+      <c r="U7" t="n">
+        <v>0</v>
+      </c>
+      <c r="V7" t="n">
+        <v>0</v>
+      </c>
+      <c r="W7" t="n">
+        <v>0</v>
+      </c>
+      <c r="X7" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y7" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA7" t="n">
+        <v>75</v>
+      </c>
+      <c r="AB7" t="inlineStr">
+        <is>
+          <t>enemy.armorbot.desc</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>enemy.armorbot.weakness</t>
+        </is>
+      </c>
+      <c r="AD7" t="inlineStr">
+        <is>
+          <t>enemy.armorbot.trait</t>
+        </is>
+      </c>
+      <c r="AE7" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="AF7" t="inlineStr">
+        <is>
+          <t>minion</t>
+        </is>
+      </c>
+      <c r="AG7" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="AH7" t="n">
+        <v>40</v>
+      </c>
+      <c r="AI7" t="inlineStr">
+        <is>
+          <t>icon_enemy_armorbot</t>
+        </is>
+      </c>
+      <c r="AJ7" t="inlineStr">
+        <is>
+          <t>foundry_shield</t>
+        </is>
+      </c>
+      <c r="AK7" t="inlineStr">
+        <is>
+          <t>#807326</t>
+        </is>
+      </c>
+      <c r="AL7" t="inlineStr">
+        <is>
+          <t>sfx_enemy_fire_heavy</t>
+        </is>
+      </c>
+      <c r="AM7" t="inlineStr">
+        <is>
+          <t>vfx_none_placeholder</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr"/>
@@ -621,6 +1640,137 @@
       <c r="F8" t="n">
         <v>15</v>
       </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>foundry</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>support</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>repair</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="L8" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="M8" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="N8" t="n">
+        <v>0</v>
+      </c>
+      <c r="O8" t="n">
+        <v>0</v>
+      </c>
+      <c r="P8" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>0</v>
+      </c>
+      <c r="R8" t="n">
+        <v>0</v>
+      </c>
+      <c r="S8" t="n">
+        <v>3</v>
+      </c>
+      <c r="T8" t="n">
+        <v>0</v>
+      </c>
+      <c r="U8" t="n">
+        <v>6</v>
+      </c>
+      <c r="V8" t="n">
+        <v>15</v>
+      </c>
+      <c r="W8" t="n">
+        <v>5</v>
+      </c>
+      <c r="X8" t="n">
+        <v>6</v>
+      </c>
+      <c r="Y8" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA8" t="n">
+        <v>90</v>
+      </c>
+      <c r="AB8" t="inlineStr">
+        <is>
+          <t>enemy.repairbot.desc</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>enemy.repairbot.weakness</t>
+        </is>
+      </c>
+      <c r="AD8" t="inlineStr">
+        <is>
+          <t>enemy.repairbot.trait</t>
+        </is>
+      </c>
+      <c r="AE8" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="AF8" t="inlineStr">
+        <is>
+          <t>minion</t>
+        </is>
+      </c>
+      <c r="AG8" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="AH8" t="n">
+        <v>20</v>
+      </c>
+      <c r="AI8" t="inlineStr">
+        <is>
+          <t>icon_enemy_repairbot</t>
+        </is>
+      </c>
+      <c r="AJ8" t="inlineStr">
+        <is>
+          <t>foundry_cross</t>
+        </is>
+      </c>
+      <c r="AK8" t="inlineStr">
+        <is>
+          <t>#338C66</t>
+        </is>
+      </c>
+      <c r="AL8" t="inlineStr">
+        <is>
+          <t>sfx_repair_beam</t>
+        </is>
+      </c>
+      <c r="AM8" t="inlineStr">
+        <is>
+          <t>vfx_none_placeholder</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr"/>
@@ -642,6 +1792,290 @@
       </c>
       <c r="F9" t="n">
         <v>0</v>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>foundry</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>boss</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>boss</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>hold_fire</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>structure,external_health,silent_fire</t>
+        </is>
+      </c>
+      <c r="L9" t="n">
+        <v>0</v>
+      </c>
+      <c r="M9" t="n">
+        <v>3</v>
+      </c>
+      <c r="N9" t="n">
+        <v>16</v>
+      </c>
+      <c r="O9" t="n">
+        <v>18</v>
+      </c>
+      <c r="P9" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>0</v>
+      </c>
+      <c r="R9" t="n">
+        <v>0</v>
+      </c>
+      <c r="S9" t="n">
+        <v>0</v>
+      </c>
+      <c r="T9" t="n">
+        <v>0</v>
+      </c>
+      <c r="U9" t="n">
+        <v>0</v>
+      </c>
+      <c r="V9" t="n">
+        <v>0</v>
+      </c>
+      <c r="W9" t="n">
+        <v>0</v>
+      </c>
+      <c r="X9" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y9" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA9" t="n">
+        <v>75</v>
+      </c>
+      <c r="AB9" t="inlineStr">
+        <is>
+          <t>enemy.core_boss.desc</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>enemy.core_boss.weakness</t>
+        </is>
+      </c>
+      <c r="AD9" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="AE9" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="AF9" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="AG9" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="AH9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI9" t="inlineStr">
+        <is>
+          <t>icon_enemy_core_boss</t>
+        </is>
+      </c>
+      <c r="AJ9" t="inlineStr">
+        <is>
+          <t>foundry_reactor</t>
+        </is>
+      </c>
+      <c r="AK9" t="inlineStr">
+        <is>
+          <t>#B38C26</t>
+        </is>
+      </c>
+      <c r="AL9" t="inlineStr">
+        <is>
+          <t>sfx_enemy_cannon</t>
+        </is>
+      </c>
+      <c r="AM9" t="inlineStr">
+        <is>
+          <t>vfx_boss_phase_placeholder</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr"/>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>enemy_core_node</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>enemy.core_node.name</t>
+        </is>
+      </c>
+      <c r="D10" t="n">
+        <v>100</v>
+      </c>
+      <c r="E10" t="n">
+        <v>0</v>
+      </c>
+      <c r="F10" t="n">
+        <v>0</v>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>foundry</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>structure</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>boss</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>structure,external_health</t>
+        </is>
+      </c>
+      <c r="L10" t="n">
+        <v>0</v>
+      </c>
+      <c r="M10" t="n">
+        <v>2</v>
+      </c>
+      <c r="N10" t="n">
+        <v>0</v>
+      </c>
+      <c r="O10" t="n">
+        <v>0</v>
+      </c>
+      <c r="P10" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>0</v>
+      </c>
+      <c r="R10" t="n">
+        <v>0</v>
+      </c>
+      <c r="S10" t="n">
+        <v>0</v>
+      </c>
+      <c r="T10" t="n">
+        <v>0</v>
+      </c>
+      <c r="U10" t="n">
+        <v>0</v>
+      </c>
+      <c r="V10" t="n">
+        <v>0</v>
+      </c>
+      <c r="W10" t="n">
+        <v>0</v>
+      </c>
+      <c r="X10" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y10" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA10" t="n">
+        <v>90</v>
+      </c>
+      <c r="AB10" t="inlineStr">
+        <is>
+          <t>enemy.core_node.desc</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>enemy.core_node.weakness</t>
+        </is>
+      </c>
+      <c r="AD10" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="AE10" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="AF10" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="AG10" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="AH10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI10" t="inlineStr">
+        <is>
+          <t>icon_enemy_core_boss</t>
+        </is>
+      </c>
+      <c r="AJ10" t="inlineStr">
+        <is>
+          <t>foundry_node</t>
+        </is>
+      </c>
+      <c r="AK10" t="inlineStr">
+        <is>
+          <t>#8C7333</t>
+        </is>
+      </c>
+      <c r="AL10" t="inlineStr">
+        <is>
+          <t>sfx_enemy_cannon</t>
+        </is>
+      </c>
+      <c r="AM10" t="inlineStr">
+        <is>
+          <t>vfx_boss_phase_placeholder</t>
+        </is>
       </c>
     </row>
   </sheetData>

--- a/Configs/GameConfig/Datas/fg/#MechEnemy-机械敌人.xlsx
+++ b/Configs/GameConfig/Datas/fg/#MechEnemy-机械敌人.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AM10"/>
+  <dimension ref="A1:AP17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -612,6 +612,21 @@
           <t>vfxId</t>
         </is>
       </c>
+      <c r="AN1" t="inlineStr">
+        <is>
+          <t>warnSeconds</t>
+        </is>
+      </c>
+      <c r="AO1" t="inlineStr">
+        <is>
+          <t>lurkSeconds</t>
+        </is>
+      </c>
+      <c r="AP1" t="inlineStr">
+        <is>
+          <t>revealRange</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -809,6 +824,21 @@
           <t>string</t>
         </is>
       </c>
+      <c r="AN2" t="inlineStr">
+        <is>
+          <t>float</t>
+        </is>
+      </c>
+      <c r="AO2" t="inlineStr">
+        <is>
+          <t>float</t>
+        </is>
+      </c>
+      <c r="AP2" t="inlineStr">
+        <is>
+          <t>float</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -988,7 +1018,7 @@
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>占位剪影(PlaceholderSilhouette):silent_orb/silent_ring/foundry_strider/foundry_shield/foundry_cross/foundry_block/foundry_node/foundry_reactor</t>
+          <t>占位剪影(PlaceholderSilhouette):silent_orb/silent_ring/foundry_strider/foundry_shield/foundry_cross/foundry_block/foundry_node/foundry_reactor/silent_node/silent_prism/silent_hunter/silent_decoy/silent_listener/silent_mind/silent_relay</t>
         </is>
       </c>
       <c r="AK3" t="inlineStr">
@@ -1004,6 +1034,21 @@
       <c r="AM3" t="inlineStr">
         <is>
           <t>行为特效ID(占位)</t>
+        </is>
+      </c>
+      <c r="AN3" t="inlineStr">
+        <is>
+          <t>专属行为预警秒数(偏折场预警 / 潜伏现形展桅 / 中继跳转亮起);0=没有专属行为</t>
+        </is>
+      </c>
+      <c r="AO3" t="inlineStr">
+        <is>
+          <t>静默潜伏:静止多少秒进入潜伏(不能被远程锁定,范围伤害命中即现形);0=不潜伏</t>
+        </is>
+      </c>
+      <c r="AP3" t="inlineStr">
+        <is>
+          <t>潜伏侦测距离(米):装有信号中继或标记器的机器在这个距离内时不能潜伏、已潜伏的现形;0=只有受伤/移动/开火才现形</t>
         </is>
       </c>
     </row>
@@ -1159,6 +1204,15 @@
           <t>vfx_none_placeholder</t>
         </is>
       </c>
+      <c r="AN4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP4" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr"/>
@@ -1312,6 +1366,15 @@
           <t>vfx_jam_field_placeholder</t>
         </is>
       </c>
+      <c r="AN5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP5" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr"/>
@@ -1465,6 +1528,15 @@
           <t>vfx_aim_line_placeholder</t>
         </is>
       </c>
+      <c r="AN6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP6" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr"/>
@@ -1618,6 +1690,15 @@
           <t>vfx_none_placeholder</t>
         </is>
       </c>
+      <c r="AN7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP7" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr"/>
@@ -1771,6 +1852,15 @@
           <t>vfx_none_placeholder</t>
         </is>
       </c>
+      <c r="AN8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP8" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr"/>
@@ -1924,6 +2014,15 @@
           <t>vfx_boss_phase_placeholder</t>
         </is>
       </c>
+      <c r="AN9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP9" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr"/>
@@ -2076,6 +2175,1149 @@
         <is>
           <t>vfx_boss_phase_placeholder</t>
         </is>
+      </c>
+      <c r="AN10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP10" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr"/>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>enemy_listen_node</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>enemy.listen_node.name</t>
+        </is>
+      </c>
+      <c r="D11" t="n">
+        <v>150</v>
+      </c>
+      <c r="E11" t="n">
+        <v>0</v>
+      </c>
+      <c r="F11" t="n">
+        <v>20</v>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>silent</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>support</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>structure,listen_amp</t>
+        </is>
+      </c>
+      <c r="L11" t="n">
+        <v>0</v>
+      </c>
+      <c r="M11" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="N11" t="n">
+        <v>0</v>
+      </c>
+      <c r="O11" t="n">
+        <v>0</v>
+      </c>
+      <c r="P11" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>0</v>
+      </c>
+      <c r="R11" t="n">
+        <v>0</v>
+      </c>
+      <c r="S11" t="n">
+        <v>0</v>
+      </c>
+      <c r="T11" t="n">
+        <v>0</v>
+      </c>
+      <c r="U11" t="n">
+        <v>16</v>
+      </c>
+      <c r="V11" t="n">
+        <v>2</v>
+      </c>
+      <c r="W11" t="n">
+        <v>0</v>
+      </c>
+      <c r="X11" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y11" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA11" t="n">
+        <v>90</v>
+      </c>
+      <c r="AB11" t="inlineStr">
+        <is>
+          <t>enemy.listen_node.desc</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>enemy.listen_node.weakness</t>
+        </is>
+      </c>
+      <c r="AD11" t="inlineStr">
+        <is>
+          <t>enemy.listen_node.trait</t>
+        </is>
+      </c>
+      <c r="AE11" t="inlineStr">
+        <is>
+          <t>func_marker</t>
+        </is>
+      </c>
+      <c r="AF11" t="inlineStr">
+        <is>
+          <t>minion</t>
+        </is>
+      </c>
+      <c r="AG11" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="AH11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI11" t="inlineStr">
+        <is>
+          <t>icon_enemy_jammer</t>
+        </is>
+      </c>
+      <c r="AJ11" t="inlineStr">
+        <is>
+          <t>silent_node</t>
+        </is>
+      </c>
+      <c r="AK11" t="inlineStr">
+        <is>
+          <t>#7A3FA8</t>
+        </is>
+      </c>
+      <c r="AL11" t="inlineStr">
+        <is>
+          <t>sfx_signal_jam</t>
+        </is>
+      </c>
+      <c r="AM11" t="inlineStr">
+        <is>
+          <t>vfx_jam_field_placeholder</t>
+        </is>
+      </c>
+      <c r="AN11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP11" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr"/>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>enemy_prism</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>enemy.prism.name</t>
+        </is>
+      </c>
+      <c r="D12" t="n">
+        <v>180</v>
+      </c>
+      <c r="E12" t="n">
+        <v>0</v>
+      </c>
+      <c r="F12" t="n">
+        <v>25</v>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>silent</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>control</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>deflect</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="L12" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="M12" t="n">
+        <v>1</v>
+      </c>
+      <c r="N12" t="n">
+        <v>8</v>
+      </c>
+      <c r="O12" t="n">
+        <v>6</v>
+      </c>
+      <c r="P12" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>0</v>
+      </c>
+      <c r="R12" t="n">
+        <v>0</v>
+      </c>
+      <c r="S12" t="n">
+        <v>6</v>
+      </c>
+      <c r="T12" t="n">
+        <v>4</v>
+      </c>
+      <c r="U12" t="n">
+        <v>5</v>
+      </c>
+      <c r="V12" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="W12" t="n">
+        <v>0</v>
+      </c>
+      <c r="X12" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y12" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA12" t="n">
+        <v>90</v>
+      </c>
+      <c r="AB12" t="inlineStr">
+        <is>
+          <t>enemy.prism.desc</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>enemy.prism.weakness</t>
+        </is>
+      </c>
+      <c r="AD12" t="inlineStr">
+        <is>
+          <t>enemy.prism.trait</t>
+        </is>
+      </c>
+      <c r="AE12" t="inlineStr">
+        <is>
+          <t>comp_gun,fw_deflect</t>
+        </is>
+      </c>
+      <c r="AF12" t="inlineStr">
+        <is>
+          <t>minion</t>
+        </is>
+      </c>
+      <c r="AG12" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="AH12" t="n">
+        <v>35</v>
+      </c>
+      <c r="AI12" t="inlineStr">
+        <is>
+          <t>icon_enemy_jammer</t>
+        </is>
+      </c>
+      <c r="AJ12" t="inlineStr">
+        <is>
+          <t>silent_prism</t>
+        </is>
+      </c>
+      <c r="AK12" t="inlineStr">
+        <is>
+          <t>#5C6FD6</t>
+        </is>
+      </c>
+      <c r="AL12" t="inlineStr">
+        <is>
+          <t>sfx_signal_jam</t>
+        </is>
+      </c>
+      <c r="AM12" t="inlineStr">
+        <is>
+          <t>vfx_jam_field_placeholder</t>
+        </is>
+      </c>
+      <c r="AN12" t="n">
+        <v>1</v>
+      </c>
+      <c r="AO12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP12" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr"/>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>enemy_echo_hunter</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>enemy.echo_hunter.name</t>
+        </is>
+      </c>
+      <c r="D13" t="n">
+        <v>110</v>
+      </c>
+      <c r="E13" t="n">
+        <v>0</v>
+      </c>
+      <c r="F13" t="n">
+        <v>30</v>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>silent</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>assassin</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>stalk</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="L13" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="M13" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="N13" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="O13" t="n">
+        <v>24</v>
+      </c>
+      <c r="P13" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="Q13" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="R13" t="n">
+        <v>10</v>
+      </c>
+      <c r="S13" t="n">
+        <v>0</v>
+      </c>
+      <c r="T13" t="n">
+        <v>0</v>
+      </c>
+      <c r="U13" t="n">
+        <v>0</v>
+      </c>
+      <c r="V13" t="n">
+        <v>0</v>
+      </c>
+      <c r="W13" t="n">
+        <v>0</v>
+      </c>
+      <c r="X13" t="n">
+        <v>14</v>
+      </c>
+      <c r="Y13" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA13" t="n">
+        <v>90</v>
+      </c>
+      <c r="AB13" t="inlineStr">
+        <is>
+          <t>enemy.echo_hunter.desc</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>enemy.echo_hunter.weakness</t>
+        </is>
+      </c>
+      <c r="AD13" t="inlineStr">
+        <is>
+          <t>enemy.echo_hunter.trait</t>
+        </is>
+      </c>
+      <c r="AE13" t="inlineStr">
+        <is>
+          <t>comp_beam,fw_orbit</t>
+        </is>
+      </c>
+      <c r="AF13" t="inlineStr">
+        <is>
+          <t>elite</t>
+        </is>
+      </c>
+      <c r="AG13" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="AH13" t="n">
+        <v>30</v>
+      </c>
+      <c r="AI13" t="inlineStr">
+        <is>
+          <t>icon_enemy_scout</t>
+        </is>
+      </c>
+      <c r="AJ13" t="inlineStr">
+        <is>
+          <t>silent_hunter</t>
+        </is>
+      </c>
+      <c r="AK13" t="inlineStr">
+        <is>
+          <t>#3A3F66</t>
+        </is>
+      </c>
+      <c r="AL13" t="inlineStr">
+        <is>
+          <t>sfx_enemy_fire</t>
+        </is>
+      </c>
+      <c r="AM13" t="inlineStr">
+        <is>
+          <t>vfx_aim_line_placeholder</t>
+        </is>
+      </c>
+      <c r="AN13" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="AO13" t="n">
+        <v>3</v>
+      </c>
+      <c r="AP13" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr"/>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>enemy_decoy_relay</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>enemy.decoy_relay.name</t>
+        </is>
+      </c>
+      <c r="D14" t="n">
+        <v>60</v>
+      </c>
+      <c r="E14" t="n">
+        <v>0</v>
+      </c>
+      <c r="F14" t="n">
+        <v>10</v>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>silent</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>decoy</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>structure,decoy</t>
+        </is>
+      </c>
+      <c r="L14" t="n">
+        <v>0</v>
+      </c>
+      <c r="M14" t="n">
+        <v>1</v>
+      </c>
+      <c r="N14" t="n">
+        <v>0</v>
+      </c>
+      <c r="O14" t="n">
+        <v>0</v>
+      </c>
+      <c r="P14" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q14" t="n">
+        <v>0</v>
+      </c>
+      <c r="R14" t="n">
+        <v>0</v>
+      </c>
+      <c r="S14" t="n">
+        <v>0</v>
+      </c>
+      <c r="T14" t="n">
+        <v>0</v>
+      </c>
+      <c r="U14" t="n">
+        <v>0</v>
+      </c>
+      <c r="V14" t="n">
+        <v>0</v>
+      </c>
+      <c r="W14" t="n">
+        <v>0</v>
+      </c>
+      <c r="X14" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y14" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA14" t="n">
+        <v>90</v>
+      </c>
+      <c r="AB14" t="inlineStr">
+        <is>
+          <t>enemy.decoy_relay.desc</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>enemy.decoy_relay.weakness</t>
+        </is>
+      </c>
+      <c r="AD14" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="AE14" t="inlineStr">
+        <is>
+          <t>func_marker</t>
+        </is>
+      </c>
+      <c r="AF14" t="inlineStr">
+        <is>
+          <t>minion</t>
+        </is>
+      </c>
+      <c r="AG14" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="AH14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI14" t="inlineStr">
+        <is>
+          <t>icon_enemy_jammer</t>
+        </is>
+      </c>
+      <c r="AJ14" t="inlineStr">
+        <is>
+          <t>silent_decoy</t>
+        </is>
+      </c>
+      <c r="AK14" t="inlineStr">
+        <is>
+          <t>#8A6FB0</t>
+        </is>
+      </c>
+      <c r="AL14" t="inlineStr">
+        <is>
+          <t>sfx_signal_jam</t>
+        </is>
+      </c>
+      <c r="AM14" t="inlineStr">
+        <is>
+          <t>vfx_none_placeholder</t>
+        </is>
+      </c>
+      <c r="AN14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP14" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr"/>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>enemy_listener</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>enemy.listener.name</t>
+        </is>
+      </c>
+      <c r="D15" t="n">
+        <v>360</v>
+      </c>
+      <c r="E15" t="n">
+        <v>0</v>
+      </c>
+      <c r="F15" t="n">
+        <v>40</v>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>silent</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>jammer</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>elite</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>sever</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="L15" t="n">
+        <v>0</v>
+      </c>
+      <c r="M15" t="n">
+        <v>1</v>
+      </c>
+      <c r="N15" t="n">
+        <v>10</v>
+      </c>
+      <c r="O15" t="n">
+        <v>8</v>
+      </c>
+      <c r="P15" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="Q15" t="n">
+        <v>0</v>
+      </c>
+      <c r="R15" t="n">
+        <v>0</v>
+      </c>
+      <c r="S15" t="n">
+        <v>6</v>
+      </c>
+      <c r="T15" t="n">
+        <v>2</v>
+      </c>
+      <c r="U15" t="n">
+        <v>14</v>
+      </c>
+      <c r="V15" t="n">
+        <v>0</v>
+      </c>
+      <c r="W15" t="n">
+        <v>0</v>
+      </c>
+      <c r="X15" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y15" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA15" t="n">
+        <v>90</v>
+      </c>
+      <c r="AB15" t="inlineStr">
+        <is>
+          <t>enemy.listener.desc</t>
+        </is>
+      </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>enemy.listener.weakness</t>
+        </is>
+      </c>
+      <c r="AD15" t="inlineStr">
+        <is>
+          <t>enemy.listener.trait</t>
+        </is>
+      </c>
+      <c r="AE15" t="inlineStr">
+        <is>
+          <t>comp_beam,fw_magnet</t>
+        </is>
+      </c>
+      <c r="AF15" t="inlineStr">
+        <is>
+          <t>elite</t>
+        </is>
+      </c>
+      <c r="AG15" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="AH15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI15" t="inlineStr">
+        <is>
+          <t>icon_enemy_jammer</t>
+        </is>
+      </c>
+      <c r="AJ15" t="inlineStr">
+        <is>
+          <t>silent_listener</t>
+        </is>
+      </c>
+      <c r="AK15" t="inlineStr">
+        <is>
+          <t>#4B2E83</t>
+        </is>
+      </c>
+      <c r="AL15" t="inlineStr">
+        <is>
+          <t>sfx_signal_jam</t>
+        </is>
+      </c>
+      <c r="AM15" t="inlineStr">
+        <is>
+          <t>vfx_aim_line_placeholder</t>
+        </is>
+      </c>
+      <c r="AN15" t="n">
+        <v>2</v>
+      </c>
+      <c r="AO15" t="n">
+        <v>4</v>
+      </c>
+      <c r="AP15" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr"/>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>enemy_mind_core</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>enemy.mind_core.name</t>
+        </is>
+      </c>
+      <c r="D16" t="n">
+        <v>900</v>
+      </c>
+      <c r="E16" t="n">
+        <v>0</v>
+      </c>
+      <c r="F16" t="n">
+        <v>0</v>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>silent</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>boss</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>boss</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>deflect</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>structure,external_health,silent_fire</t>
+        </is>
+      </c>
+      <c r="L16" t="n">
+        <v>0</v>
+      </c>
+      <c r="M16" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="N16" t="n">
+        <v>18</v>
+      </c>
+      <c r="O16" t="n">
+        <v>10</v>
+      </c>
+      <c r="P16" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="Q16" t="n">
+        <v>0</v>
+      </c>
+      <c r="R16" t="n">
+        <v>0</v>
+      </c>
+      <c r="S16" t="n">
+        <v>6</v>
+      </c>
+      <c r="T16" t="n">
+        <v>4</v>
+      </c>
+      <c r="U16" t="n">
+        <v>80</v>
+      </c>
+      <c r="V16" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="W16" t="n">
+        <v>0</v>
+      </c>
+      <c r="X16" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y16" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA16" t="n">
+        <v>90</v>
+      </c>
+      <c r="AB16" t="inlineStr">
+        <is>
+          <t>enemy.mind_core.desc</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>enemy.mind_core.weakness</t>
+        </is>
+      </c>
+      <c r="AD16" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="AE16" t="inlineStr">
+        <is>
+          <t>fw_swarm,fw_marktag</t>
+        </is>
+      </c>
+      <c r="AF16" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="AG16" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="AH16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI16" t="inlineStr">
+        <is>
+          <t>icon_enemy_core_boss</t>
+        </is>
+      </c>
+      <c r="AJ16" t="inlineStr">
+        <is>
+          <t>silent_mind</t>
+        </is>
+      </c>
+      <c r="AK16" t="inlineStr">
+        <is>
+          <t>#6B3FC2</t>
+        </is>
+      </c>
+      <c r="AL16" t="inlineStr">
+        <is>
+          <t>sfx_boss_phase</t>
+        </is>
+      </c>
+      <c r="AM16" t="inlineStr">
+        <is>
+          <t>vfx_boss_phase_placeholder</t>
+        </is>
+      </c>
+      <c r="AN16" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AO16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP16" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr"/>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>enemy_mind_relay</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>enemy.mind_relay.name</t>
+        </is>
+      </c>
+      <c r="D17" t="n">
+        <v>80</v>
+      </c>
+      <c r="E17" t="n">
+        <v>0</v>
+      </c>
+      <c r="F17" t="n">
+        <v>0</v>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>silent</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>structure</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>boss</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>structure,external_health</t>
+        </is>
+      </c>
+      <c r="L17" t="n">
+        <v>0</v>
+      </c>
+      <c r="M17" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="N17" t="n">
+        <v>0</v>
+      </c>
+      <c r="O17" t="n">
+        <v>0</v>
+      </c>
+      <c r="P17" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q17" t="n">
+        <v>0</v>
+      </c>
+      <c r="R17" t="n">
+        <v>0</v>
+      </c>
+      <c r="S17" t="n">
+        <v>0</v>
+      </c>
+      <c r="T17" t="n">
+        <v>0</v>
+      </c>
+      <c r="U17" t="n">
+        <v>0</v>
+      </c>
+      <c r="V17" t="n">
+        <v>0</v>
+      </c>
+      <c r="W17" t="n">
+        <v>0</v>
+      </c>
+      <c r="X17" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y17" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA17" t="n">
+        <v>90</v>
+      </c>
+      <c r="AB17" t="inlineStr">
+        <is>
+          <t>enemy.mind_relay.desc</t>
+        </is>
+      </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>enemy.mind_relay.weakness</t>
+        </is>
+      </c>
+      <c r="AD17" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="AE17" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="AF17" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="AG17" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="AH17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI17" t="inlineStr">
+        <is>
+          <t>icon_enemy_core_boss</t>
+        </is>
+      </c>
+      <c r="AJ17" t="inlineStr">
+        <is>
+          <t>silent_relay</t>
+        </is>
+      </c>
+      <c r="AK17" t="inlineStr">
+        <is>
+          <t>#7F66B3</t>
+        </is>
+      </c>
+      <c r="AL17" t="inlineStr">
+        <is>
+          <t>sfx_signal_jam</t>
+        </is>
+      </c>
+      <c r="AM17" t="inlineStr">
+        <is>
+          <t>vfx_boss_phase_placeholder</t>
+        </is>
+      </c>
+      <c r="AN17" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AO17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP17" t="n">
+        <v>0</v>
       </c>
     </row>
   </sheetData>

--- a/Configs/GameConfig/Datas/fg/#MechEnemy-机械敌人.xlsx
+++ b/Configs/GameConfig/Datas/fg/#MechEnemy-机械敌人.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AP17"/>
+  <dimension ref="A1:AX22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -627,6 +627,46 @@
           <t>revealRange</t>
         </is>
       </c>
+      <c r="AQ1" t="inlineStr">
+        <is>
+          <t>salvoCount</t>
+        </is>
+      </c>
+      <c r="AR1" t="inlineStr">
+        <is>
+          <t>salvoGap</t>
+        </is>
+      </c>
+      <c r="AS1" t="inlineStr">
+        <is>
+          <t>minRange</t>
+        </is>
+      </c>
+      <c r="AT1" t="inlineStr">
+        <is>
+          <t>deploySeconds</t>
+        </is>
+      </c>
+      <c r="AU1" t="inlineStr">
+        <is>
+          <t>rearBonus</t>
+        </is>
+      </c>
+      <c r="AV1" t="inlineStr">
+        <is>
+          <t>chargeSpeed</t>
+        </is>
+      </c>
+      <c r="AW1" t="inlineStr">
+        <is>
+          <t>turnRate</t>
+        </is>
+      </c>
+      <c r="AX1" t="inlineStr">
+        <is>
+          <t>maxPlaced</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -839,6 +879,46 @@
           <t>float</t>
         </is>
       </c>
+      <c r="AQ2" t="inlineStr">
+        <is>
+          <t>float</t>
+        </is>
+      </c>
+      <c r="AR2" t="inlineStr">
+        <is>
+          <t>float</t>
+        </is>
+      </c>
+      <c r="AS2" t="inlineStr">
+        <is>
+          <t>float</t>
+        </is>
+      </c>
+      <c r="AT2" t="inlineStr">
+        <is>
+          <t>float</t>
+        </is>
+      </c>
+      <c r="AU2" t="inlineStr">
+        <is>
+          <t>float</t>
+        </is>
+      </c>
+      <c r="AV2" t="inlineStr">
+        <is>
+          <t>float</t>
+        </is>
+      </c>
+      <c r="AW2" t="inlineStr">
+        <is>
+          <t>float</t>
+        </is>
+      </c>
+      <c r="AX2" t="inlineStr">
+        <is>
+          <t>float</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -1018,7 +1098,7 @@
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>占位剪影(PlaceholderSilhouette):silent_orb/silent_ring/foundry_strider/foundry_shield/foundry_cross/foundry_block/foundry_node/foundry_reactor/silent_node/silent_prism/silent_hunter/silent_decoy/silent_listener/silent_mind/silent_relay</t>
+          <t>占位剪影(PlaceholderSilhouette):silent_orb/silent_ring/foundry_strider/foundry_shield/foundry_cross/foundry_block/foundry_node/foundry_reactor/silent_node/silent_prism/silent_hunter/silent_decoy/silent_listener/silent_mind/silent_relay/foundry_airburst/foundry_aa/foundry_minelayer/foundry_loader/foundry_siege_heavy</t>
         </is>
       </c>
       <c r="AK3" t="inlineStr">
@@ -1049,6 +1129,46 @@
       <c r="AP3" t="inlineStr">
         <is>
           <t>潜伏侦测距离(米):装有信号中继或标记器的机器在这个距离内时不能潜伏、已潜伏的现形;0=只有受伤/移动/开火才现形</t>
+        </is>
+      </c>
+      <c r="AQ3" t="inlineStr">
+        <is>
+          <t>齐射弹幕:一轮几发(整数;首领的对空形态也读它);0=不齐射</t>
+        </is>
+      </c>
+      <c r="AR3" t="inlineStr">
+        <is>
+          <t>齐射弹幕:一轮里每发之间的间隔(秒)</t>
+        </is>
+      </c>
+      <c r="AS3" t="inlineStr">
+        <is>
+          <t>高抛曲射的近距盲区(米):目标比这更近就打不到;0=没有盲区</t>
+        </is>
+      </c>
+      <c r="AT3" t="inlineStr">
+        <is>
+          <t>架炮驻锄:开火前放下支腿、抬升炮口要多少秒(架设中被击退 / 冻结就回到未架设);0=不用架设</t>
+        </is>
+      </c>
+      <c r="AU3" t="inlineStr">
+        <is>
+          <t>背部弱点:从侧后命中时伤害额外 +本值(0.5=+50%);0=没有</t>
+        </is>
+      </c>
+      <c r="AV3" t="inlineStr">
+        <is>
+          <t>正面推进冲锋:冲锋速度(米/秒);0=不冲锋</t>
+        </is>
+      </c>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>转向速度(度/秒;正面推进:转向半径大);0=瞬间转向</t>
+        </is>
+      </c>
+      <c r="AX3" t="inlineStr">
+        <is>
+          <t>布雷:同时最多几颗雷(整数);0=不布雷</t>
         </is>
       </c>
     </row>
@@ -1213,6 +1333,30 @@
       <c r="AP4" t="n">
         <v>0</v>
       </c>
+      <c r="AQ4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX4" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr"/>
@@ -1375,6 +1519,30 @@
       <c r="AP5" t="n">
         <v>0</v>
       </c>
+      <c r="AQ5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX5" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr"/>
@@ -1537,6 +1705,30 @@
       <c r="AP6" t="n">
         <v>0</v>
       </c>
+      <c r="AQ6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS6" t="n">
+        <v>4</v>
+      </c>
+      <c r="AT6" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX6" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr"/>
@@ -1699,6 +1891,30 @@
       <c r="AP7" t="n">
         <v>0</v>
       </c>
+      <c r="AQ7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX7" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr"/>
@@ -1861,6 +2077,30 @@
       <c r="AP8" t="n">
         <v>0</v>
       </c>
+      <c r="AQ8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX8" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr"/>
@@ -1930,7 +2170,7 @@
         <v>0</v>
       </c>
       <c r="S9" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="T9" t="n">
         <v>0</v>
@@ -1973,19 +2213,19 @@
       </c>
       <c r="AE9" t="inlineStr">
         <is>
+          <t>fw_overload,fw_capacitor</t>
+        </is>
+      </c>
+      <c r="AF9" t="inlineStr">
+        <is>
           <t>none</t>
         </is>
       </c>
-      <c r="AF9" t="inlineStr">
+      <c r="AG9" t="inlineStr">
         <is>
           <t>none</t>
         </is>
       </c>
-      <c r="AG9" t="inlineStr">
-        <is>
-          <t>none</t>
-        </is>
-      </c>
       <c r="AH9" t="n">
         <v>0</v>
       </c>
@@ -2015,12 +2255,36 @@
         </is>
       </c>
       <c r="AN9" t="n">
-        <v>0</v>
+        <v>0.8</v>
       </c>
       <c r="AO9" t="n">
         <v>0</v>
       </c>
       <c r="AP9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ9" t="n">
+        <v>6</v>
+      </c>
+      <c r="AR9" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="AS9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX9" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2185,6 +2449,30 @@
       <c r="AP10" t="n">
         <v>0</v>
       </c>
+      <c r="AQ10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX10" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr"/>
@@ -2347,6 +2635,30 @@
       <c r="AP11" t="n">
         <v>0</v>
       </c>
+      <c r="AQ11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX11" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr"/>
@@ -2509,6 +2821,30 @@
       <c r="AP12" t="n">
         <v>0</v>
       </c>
+      <c r="AQ12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX12" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr"/>
@@ -2671,6 +3007,30 @@
       <c r="AP13" t="n">
         <v>8</v>
       </c>
+      <c r="AQ13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX13" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr"/>
@@ -2833,6 +3193,30 @@
       <c r="AP14" t="n">
         <v>0</v>
       </c>
+      <c r="AQ14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX14" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr"/>
@@ -2995,6 +3379,30 @@
       <c r="AP15" t="n">
         <v>8</v>
       </c>
+      <c r="AQ15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX15" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr"/>
@@ -3157,6 +3565,30 @@
       <c r="AP16" t="n">
         <v>0</v>
       </c>
+      <c r="AQ16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX16" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr"/>
@@ -3317,6 +3749,960 @@
         <v>0</v>
       </c>
       <c r="AP17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX17" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr"/>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>enemy_airburst</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>enemy.airburst.name</t>
+        </is>
+      </c>
+      <c r="D18" t="n">
+        <v>220</v>
+      </c>
+      <c r="E18" t="n">
+        <v>0</v>
+      </c>
+      <c r="F18" t="n">
+        <v>25</v>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>foundry</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>artillery</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>salvo</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>structure,airburst,assembled</t>
+        </is>
+      </c>
+      <c r="L18" t="n">
+        <v>0</v>
+      </c>
+      <c r="M18" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="N18" t="n">
+        <v>16</v>
+      </c>
+      <c r="O18" t="n">
+        <v>14</v>
+      </c>
+      <c r="P18" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q18" t="n">
+        <v>0</v>
+      </c>
+      <c r="R18" t="n">
+        <v>0</v>
+      </c>
+      <c r="S18" t="n">
+        <v>6</v>
+      </c>
+      <c r="T18" t="n">
+        <v>0</v>
+      </c>
+      <c r="U18" t="n">
+        <v>3</v>
+      </c>
+      <c r="V18" t="n">
+        <v>0</v>
+      </c>
+      <c r="W18" t="n">
+        <v>0</v>
+      </c>
+      <c r="X18" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y18" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA18" t="n">
+        <v>90</v>
+      </c>
+      <c r="AB18" t="inlineStr">
+        <is>
+          <t>enemy.airburst.desc</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>enemy.airburst.weakness</t>
+        </is>
+      </c>
+      <c r="AD18" t="inlineStr">
+        <is>
+          <t>enemy.airburst.trait</t>
+        </is>
+      </c>
+      <c r="AE18" t="inlineStr">
+        <is>
+          <t>comp_cannon,fw_delayfuse</t>
+        </is>
+      </c>
+      <c r="AF18" t="inlineStr">
+        <is>
+          <t>minion</t>
+        </is>
+      </c>
+      <c r="AG18" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="AH18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI18" t="inlineStr">
+        <is>
+          <t>icon_enemy_strider</t>
+        </is>
+      </c>
+      <c r="AJ18" t="inlineStr">
+        <is>
+          <t>foundry_airburst</t>
+        </is>
+      </c>
+      <c r="AK18" t="inlineStr">
+        <is>
+          <t>#C2581E</t>
+        </is>
+      </c>
+      <c r="AL18" t="inlineStr">
+        <is>
+          <t>sfx_enemy_cannon</t>
+        </is>
+      </c>
+      <c r="AM18" t="inlineStr">
+        <is>
+          <t>vfx_aim_line_placeholder</t>
+        </is>
+      </c>
+      <c r="AN18" t="n">
+        <v>1</v>
+      </c>
+      <c r="AO18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ18" t="n">
+        <v>3</v>
+      </c>
+      <c r="AR18" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="AS18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX18" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr"/>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>enemy_minelayer</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>enemy.minelayer.name</t>
+        </is>
+      </c>
+      <c r="D19" t="n">
+        <v>140</v>
+      </c>
+      <c r="E19" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="F19" t="n">
+        <v>25</v>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>foundry</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>control</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>minelay</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>assembled</t>
+        </is>
+      </c>
+      <c r="L19" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="M19" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="N19" t="n">
+        <v>0</v>
+      </c>
+      <c r="O19" t="n">
+        <v>0</v>
+      </c>
+      <c r="P19" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q19" t="n">
+        <v>0</v>
+      </c>
+      <c r="R19" t="n">
+        <v>0</v>
+      </c>
+      <c r="S19" t="n">
+        <v>7</v>
+      </c>
+      <c r="T19" t="n">
+        <v>0</v>
+      </c>
+      <c r="U19" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="V19" t="n">
+        <v>30</v>
+      </c>
+      <c r="W19" t="n">
+        <v>6</v>
+      </c>
+      <c r="X19" t="n">
+        <v>8</v>
+      </c>
+      <c r="Y19" t="n">
+        <v>5</v>
+      </c>
+      <c r="Z19" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="AA19" t="n">
+        <v>90</v>
+      </c>
+      <c r="AB19" t="inlineStr">
+        <is>
+          <t>enemy.minelayer.desc</t>
+        </is>
+      </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>enemy.minelayer.weakness</t>
+        </is>
+      </c>
+      <c r="AD19" t="inlineStr">
+        <is>
+          <t>enemy.minelayer.trait</t>
+        </is>
+      </c>
+      <c r="AE19" t="inlineStr">
+        <is>
+          <t>comp_pulser,fw_delayfuse</t>
+        </is>
+      </c>
+      <c r="AF19" t="inlineStr">
+        <is>
+          <t>minion</t>
+        </is>
+      </c>
+      <c r="AG19" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="AH19" t="n">
+        <v>30</v>
+      </c>
+      <c r="AI19" t="inlineStr">
+        <is>
+          <t>icon_enemy_repairbot</t>
+        </is>
+      </c>
+      <c r="AJ19" t="inlineStr">
+        <is>
+          <t>foundry_minelayer</t>
+        </is>
+      </c>
+      <c r="AK19" t="inlineStr">
+        <is>
+          <t>#9A6B2F</t>
+        </is>
+      </c>
+      <c r="AL19" t="inlineStr">
+        <is>
+          <t>sfx_enemy_fire</t>
+        </is>
+      </c>
+      <c r="AM19" t="inlineStr">
+        <is>
+          <t>vfx_none_placeholder</t>
+        </is>
+      </c>
+      <c r="AN19" t="n">
+        <v>1</v>
+      </c>
+      <c r="AO19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX19" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr"/>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>enemy_aa_gun</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>enemy.aa_gun.name</t>
+        </is>
+      </c>
+      <c r="D20" t="n">
+        <v>260</v>
+      </c>
+      <c r="E20" t="n">
+        <v>0</v>
+      </c>
+      <c r="F20" t="n">
+        <v>25</v>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>foundry</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>artillery</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>salvo</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>structure,anti_air,assembled</t>
+        </is>
+      </c>
+      <c r="L20" t="n">
+        <v>0</v>
+      </c>
+      <c r="M20" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="N20" t="n">
+        <v>20</v>
+      </c>
+      <c r="O20" t="n">
+        <v>10</v>
+      </c>
+      <c r="P20" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q20" t="n">
+        <v>0</v>
+      </c>
+      <c r="R20" t="n">
+        <v>0</v>
+      </c>
+      <c r="S20" t="n">
+        <v>5</v>
+      </c>
+      <c r="T20" t="n">
+        <v>0</v>
+      </c>
+      <c r="U20" t="n">
+        <v>0</v>
+      </c>
+      <c r="V20" t="n">
+        <v>0</v>
+      </c>
+      <c r="W20" t="n">
+        <v>0</v>
+      </c>
+      <c r="X20" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y20" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA20" t="n">
+        <v>90</v>
+      </c>
+      <c r="AB20" t="inlineStr">
+        <is>
+          <t>enemy.aa_gun.desc</t>
+        </is>
+      </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>enemy.aa_gun.weakness</t>
+        </is>
+      </c>
+      <c r="AD20" t="inlineStr">
+        <is>
+          <t>enemy.aa_gun.trait</t>
+        </is>
+      </c>
+      <c r="AE20" t="inlineStr">
+        <is>
+          <t>comp_gun,fw_homing</t>
+        </is>
+      </c>
+      <c r="AF20" t="inlineStr">
+        <is>
+          <t>minion</t>
+        </is>
+      </c>
+      <c r="AG20" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="AH20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI20" t="inlineStr">
+        <is>
+          <t>icon_enemy_strider</t>
+        </is>
+      </c>
+      <c r="AJ20" t="inlineStr">
+        <is>
+          <t>foundry_aa</t>
+        </is>
+      </c>
+      <c r="AK20" t="inlineStr">
+        <is>
+          <t>#A0522D</t>
+        </is>
+      </c>
+      <c r="AL20" t="inlineStr">
+        <is>
+          <t>sfx_enemy_cannon</t>
+        </is>
+      </c>
+      <c r="AM20" t="inlineStr">
+        <is>
+          <t>vfx_aim_line_placeholder</t>
+        </is>
+      </c>
+      <c r="AN20" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="AO20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ20" t="n">
+        <v>4</v>
+      </c>
+      <c r="AR20" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="AS20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX20" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr"/>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>enemy_loader</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>enemy.loader.name</t>
+        </is>
+      </c>
+      <c r="D21" t="n">
+        <v>90</v>
+      </c>
+      <c r="E21" t="n">
+        <v>0</v>
+      </c>
+      <c r="F21" t="n">
+        <v>15</v>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>foundry</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>support</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>reload</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>assembled</t>
+        </is>
+      </c>
+      <c r="L21" t="n">
+        <v>2</v>
+      </c>
+      <c r="M21" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="N21" t="n">
+        <v>0</v>
+      </c>
+      <c r="O21" t="n">
+        <v>0</v>
+      </c>
+      <c r="P21" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q21" t="n">
+        <v>0</v>
+      </c>
+      <c r="R21" t="n">
+        <v>0</v>
+      </c>
+      <c r="S21" t="n">
+        <v>0</v>
+      </c>
+      <c r="T21" t="n">
+        <v>0</v>
+      </c>
+      <c r="U21" t="n">
+        <v>8</v>
+      </c>
+      <c r="V21" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="W21" t="n">
+        <v>5</v>
+      </c>
+      <c r="X21" t="n">
+        <v>5</v>
+      </c>
+      <c r="Y21" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA21" t="n">
+        <v>90</v>
+      </c>
+      <c r="AB21" t="inlineStr">
+        <is>
+          <t>enemy.loader.desc</t>
+        </is>
+      </c>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>enemy.loader.weakness</t>
+        </is>
+      </c>
+      <c r="AD21" t="inlineStr">
+        <is>
+          <t>enemy.loader.trait</t>
+        </is>
+      </c>
+      <c r="AE21" t="inlineStr">
+        <is>
+          <t>comp_repairbeam</t>
+        </is>
+      </c>
+      <c r="AF21" t="inlineStr">
+        <is>
+          <t>minion</t>
+        </is>
+      </c>
+      <c r="AG21" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="AH21" t="n">
+        <v>18</v>
+      </c>
+      <c r="AI21" t="inlineStr">
+        <is>
+          <t>icon_enemy_repairbot</t>
+        </is>
+      </c>
+      <c r="AJ21" t="inlineStr">
+        <is>
+          <t>foundry_loader</t>
+        </is>
+      </c>
+      <c r="AK21" t="inlineStr">
+        <is>
+          <t>#4F8A5B</t>
+        </is>
+      </c>
+      <c r="AL21" t="inlineStr">
+        <is>
+          <t>sfx_repair_beam</t>
+        </is>
+      </c>
+      <c r="AM21" t="inlineStr">
+        <is>
+          <t>vfx_none_placeholder</t>
+        </is>
+      </c>
+      <c r="AN21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX21" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr"/>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>enemy_siege_heavy</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>enemy.siege_heavy.name</t>
+        </is>
+      </c>
+      <c r="D22" t="n">
+        <v>700</v>
+      </c>
+      <c r="E22" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="F22" t="n">
+        <v>60</v>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>foundry</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>armor</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>elite</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>charge</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>adapt_heat,assembled</t>
+        </is>
+      </c>
+      <c r="L22" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="M22" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="N22" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="O22" t="n">
+        <v>24</v>
+      </c>
+      <c r="P22" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q22" t="n">
+        <v>0</v>
+      </c>
+      <c r="R22" t="n">
+        <v>16</v>
+      </c>
+      <c r="S22" t="n">
+        <v>9</v>
+      </c>
+      <c r="T22" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="U22" t="n">
+        <v>0</v>
+      </c>
+      <c r="V22" t="n">
+        <v>3</v>
+      </c>
+      <c r="W22" t="n">
+        <v>0</v>
+      </c>
+      <c r="X22" t="n">
+        <v>30</v>
+      </c>
+      <c r="Y22" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA22" t="n">
+        <v>60</v>
+      </c>
+      <c r="AB22" t="inlineStr">
+        <is>
+          <t>enemy.siege_heavy.desc</t>
+        </is>
+      </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>enemy.siege_heavy.weakness</t>
+        </is>
+      </c>
+      <c r="AD22" t="inlineStr">
+        <is>
+          <t>enemy.siege_heavy.trait</t>
+        </is>
+      </c>
+      <c r="AE22" t="inlineStr">
+        <is>
+          <t>comp_ram,fw_wallslam</t>
+        </is>
+      </c>
+      <c r="AF22" t="inlineStr">
+        <is>
+          <t>elite</t>
+        </is>
+      </c>
+      <c r="AG22" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="AH22" t="n">
+        <v>80</v>
+      </c>
+      <c r="AI22" t="inlineStr">
+        <is>
+          <t>icon_enemy_armorbot</t>
+        </is>
+      </c>
+      <c r="AJ22" t="inlineStr">
+        <is>
+          <t>foundry_siege_heavy</t>
+        </is>
+      </c>
+      <c r="AK22" t="inlineStr">
+        <is>
+          <t>#6E5A1E</t>
+        </is>
+      </c>
+      <c r="AL22" t="inlineStr">
+        <is>
+          <t>sfx_enemy_fire_heavy</t>
+        </is>
+      </c>
+      <c r="AM22" t="inlineStr">
+        <is>
+          <t>vfx_boss_phase_placeholder</t>
+        </is>
+      </c>
+      <c r="AN22" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="AO22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU22" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="AV22" t="n">
+        <v>9</v>
+      </c>
+      <c r="AW22" t="n">
+        <v>45</v>
+      </c>
+      <c r="AX22" t="n">
         <v>0</v>
       </c>
     </row>

--- a/Configs/GameConfig/Datas/fg/#MechEnemy-机械敌人.xlsx
+++ b/Configs/GameConfig/Datas/fg/#MechEnemy-机械敌人.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AX22"/>
+  <dimension ref="A1:AY22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -667,6 +667,11 @@
           <t>maxPlaced</t>
         </is>
       </c>
+      <c r="AY1" t="inlineStr">
+        <is>
+          <t>codexLinks</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -919,6 +924,11 @@
           <t>float</t>
         </is>
       </c>
+      <c r="AY2" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -1169,6 +1179,11 @@
       <c r="AX3" t="inlineStr">
         <is>
           <t>布雷:同时最多几颗雷(整数);0=不布雷</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr">
+        <is>
+          <t>FG9-UX-01 图鉴互链:逗号分隔的图鉴条目ID(reaction:/comp:/fw:/enemy:/codex.*),敌人 ↔ 弱点相关的反应 / 组件 / 机制;none=只链阵营</t>
         </is>
       </c>
     </row>
@@ -1357,6 +1372,11 @@
       <c r="AX4" t="n">
         <v>0</v>
       </c>
+      <c r="AY4" t="inlineStr">
+        <is>
+          <t>comp:comp_gun</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr"/>
@@ -1543,6 +1563,11 @@
       <c r="AX5" t="n">
         <v>0</v>
       </c>
+      <c r="AY5" t="inlineStr">
+        <is>
+          <t>comp:comp_gun,codex.signal.exposure</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr"/>
@@ -1729,6 +1754,11 @@
       <c r="AX6" t="n">
         <v>0</v>
       </c>
+      <c r="AY6" t="inlineStr">
+        <is>
+          <t>comp:comp_cannon</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr"/>
@@ -1915,6 +1945,11 @@
       <c r="AX7" t="n">
         <v>0</v>
       </c>
+      <c r="AY7" t="inlineStr">
+        <is>
+          <t>reaction:reaction_meltoverload</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr"/>
@@ -2101,6 +2136,11 @@
       <c r="AX8" t="n">
         <v>0</v>
       </c>
+      <c r="AY8" t="inlineStr">
+        <is>
+          <t>enemy:enemy_armorbot</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr"/>
@@ -2287,6 +2327,11 @@
       <c r="AX9" t="n">
         <v>0</v>
       </c>
+      <c r="AY9" t="inlineStr">
+        <is>
+          <t>enemy:enemy_core_node,codex.intel.boss_weakness</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr"/>
@@ -2473,6 +2518,11 @@
       <c r="AX10" t="n">
         <v>0</v>
       </c>
+      <c r="AY10" t="inlineStr">
+        <is>
+          <t>enemy:enemy_core_boss</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr"/>
@@ -2659,6 +2709,11 @@
       <c r="AX11" t="n">
         <v>0</v>
       </c>
+      <c r="AY11" t="inlineStr">
+        <is>
+          <t>codex.signal.exposure,codex.signal.core_firmware</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr"/>
@@ -2845,6 +2900,11 @@
       <c r="AX12" t="n">
         <v>0</v>
       </c>
+      <c r="AY12" t="inlineStr">
+        <is>
+          <t>comp:comp_ram</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr"/>
@@ -3031,6 +3091,11 @@
       <c r="AX13" t="n">
         <v>0</v>
       </c>
+      <c r="AY13" t="inlineStr">
+        <is>
+          <t>comp:func_marker,comp:struct_relay</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr"/>
@@ -3217,6 +3282,11 @@
       <c r="AX14" t="n">
         <v>0</v>
       </c>
+      <c r="AY14" t="inlineStr">
+        <is>
+          <t>codex.intel.listening_post</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr"/>
@@ -3403,6 +3473,11 @@
       <c r="AX15" t="n">
         <v>0</v>
       </c>
+      <c r="AY15" t="inlineStr">
+        <is>
+          <t>codex.signal.uplink</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr"/>
@@ -3589,6 +3664,11 @@
       <c r="AX16" t="n">
         <v>0</v>
       </c>
+      <c r="AY16" t="inlineStr">
+        <is>
+          <t>enemy:enemy_mind_relay,comp:func_marker,codex.intel.listening_post</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr"/>
@@ -3775,6 +3855,11 @@
       <c r="AX17" t="n">
         <v>0</v>
       </c>
+      <c r="AY17" t="inlineStr">
+        <is>
+          <t>enemy:enemy_mind_core,comp:func_marker</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr"/>
@@ -3961,6 +4046,11 @@
       <c r="AX18" t="n">
         <v>0</v>
       </c>
+      <c r="AY18" t="inlineStr">
+        <is>
+          <t>comp:comp_gun</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr"/>
@@ -4147,6 +4237,11 @@
       <c r="AX19" t="n">
         <v>4</v>
       </c>
+      <c r="AY19" t="inlineStr">
+        <is>
+          <t>comp:comp_gun</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr"/>
@@ -4333,6 +4428,11 @@
       <c r="AX20" t="n">
         <v>0</v>
       </c>
+      <c r="AY20" t="inlineStr">
+        <is>
+          <t>codex.expedition.drop</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr"/>
@@ -4519,6 +4619,11 @@
       <c r="AX21" t="n">
         <v>0</v>
       </c>
+      <c r="AY21" t="inlineStr">
+        <is>
+          <t>enemy:enemy_airburst,enemy:enemy_strider</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr"/>
@@ -4704,6 +4809,11 @@
       </c>
       <c r="AX22" t="n">
         <v>0</v>
+      </c>
+      <c r="AY22" t="inlineStr">
+        <is>
+          <t>reaction:reaction_meltoverload</t>
+        </is>
       </c>
     </row>
   </sheetData>

--- a/Configs/GameConfig/Datas/fg/#MechEnemy-机械敌人.xlsx
+++ b/Configs/GameConfig/Datas/fg/#MechEnemy-机械敌人.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY22"/>
+  <dimension ref="A1:BL28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -669,6 +669,71 @@
       </c>
       <c r="AY1" t="inlineStr">
         <is>
+          <t>sprayCone</t>
+        </is>
+      </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>poolRadius</t>
+        </is>
+      </c>
+      <c r="BA1" t="inlineStr">
+        <is>
+          <t>poolSeconds</t>
+        </is>
+      </c>
+      <c r="BB1" t="inlineStr">
+        <is>
+          <t>poolDps</t>
+        </is>
+      </c>
+      <c r="BC1" t="inlineStr">
+        <is>
+          <t>chill</t>
+        </is>
+      </c>
+      <c r="BD1" t="inlineStr">
+        <is>
+          <t>statusTag</t>
+        </is>
+      </c>
+      <c r="BE1" t="inlineStr">
+        <is>
+          <t>statusSeconds</t>
+        </is>
+      </c>
+      <c r="BF1" t="inlineStr">
+        <is>
+          <t>deflagMult</t>
+        </is>
+      </c>
+      <c r="BG1" t="inlineStr">
+        <is>
+          <t>splitCount</t>
+        </is>
+      </c>
+      <c r="BH1" t="inlineStr">
+        <is>
+          <t>splitHp</t>
+        </is>
+      </c>
+      <c r="BI1" t="inlineStr">
+        <is>
+          <t>splitSpeed</t>
+        </is>
+      </c>
+      <c r="BJ1" t="inlineStr">
+        <is>
+          <t>splitLife</t>
+        </is>
+      </c>
+      <c r="BK1" t="inlineStr">
+        <is>
+          <t>splitDps</t>
+        </is>
+      </c>
+      <c r="BL1" t="inlineStr">
+        <is>
           <t>codexLinks</t>
         </is>
       </c>
@@ -926,6 +991,71 @@
       </c>
       <c r="AY2" t="inlineStr">
         <is>
+          <t>float</t>
+        </is>
+      </c>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>float</t>
+        </is>
+      </c>
+      <c r="BA2" t="inlineStr">
+        <is>
+          <t>float</t>
+        </is>
+      </c>
+      <c r="BB2" t="inlineStr">
+        <is>
+          <t>float</t>
+        </is>
+      </c>
+      <c r="BC2" t="inlineStr">
+        <is>
+          <t>float</t>
+        </is>
+      </c>
+      <c r="BD2" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="BE2" t="inlineStr">
+        <is>
+          <t>float</t>
+        </is>
+      </c>
+      <c r="BF2" t="inlineStr">
+        <is>
+          <t>float</t>
+        </is>
+      </c>
+      <c r="BG2" t="inlineStr">
+        <is>
+          <t>float</t>
+        </is>
+      </c>
+      <c r="BH2" t="inlineStr">
+        <is>
+          <t>float</t>
+        </is>
+      </c>
+      <c r="BI2" t="inlineStr">
+        <is>
+          <t>float</t>
+        </is>
+      </c>
+      <c r="BJ2" t="inlineStr">
+        <is>
+          <t>float</t>
+        </is>
+      </c>
+      <c r="BK2" t="inlineStr">
+        <is>
+          <t>float</t>
+        </is>
+      </c>
+      <c r="BL2" t="inlineStr">
+        <is>
           <t>string</t>
         </is>
       </c>
@@ -1108,7 +1238,7 @@
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>占位剪影(PlaceholderSilhouette):silent_orb/silent_ring/foundry_strider/foundry_shield/foundry_cross/foundry_block/foundry_node/foundry_reactor/silent_node/silent_prism/silent_hunter/silent_decoy/silent_listener/silent_mind/silent_relay/foundry_airburst/foundry_aa/foundry_minelayer/foundry_loader/foundry_siege_heavy</t>
+          <t>占位剪影(PlaceholderSilhouette):silent_orb/silent_ring/foundry_strider/foundry_shield/foundry_cross/foundry_block/foundry_node/foundry_reactor/silent_node/silent_prism/silent_hunter/silent_decoy/silent_listener/silent_mind/silent_relay/foundry_airburst/foundry_aa/foundry_minelayer/foundry_loader/foundry_siege_heavy/clarity_sprayer/clarity_crawler/clarity_pump/clarity_drone/clarity_swarm/clarity_tank</t>
         </is>
       </c>
       <c r="AK3" t="inlineStr">
@@ -1182,6 +1312,71 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr">
+        <is>
+          <t>喷淋锥形半角 / 枢轴喷淋臂半宽(度);0=没有</t>
+        </is>
+      </c>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>喷淋池 / 油迹 / 分裂液接触的半径(米);0=不留池</t>
+        </is>
+      </c>
+      <c r="BA3" t="inlineStr">
+        <is>
+          <t>喷淋池存留(秒);0=不留池</t>
+        </is>
+      </c>
+      <c r="BB3" t="inlineStr">
+        <is>
+          <t>喷淋池每秒伤害(难度倍率另乘)</t>
+        </is>
+      </c>
+      <c r="BC3" t="inlineStr">
+        <is>
+          <t>液氮:每次喷中给目标加的受寒(0~1,满 1 冻结;液氮池每节拍 × clarity.pool.chill_tick_frac);0=没有</t>
+        </is>
+      </c>
+      <c r="BD3" t="inlineStr">
+        <is>
+          <t>喷淋 / 喷灌 / 油迹 / 分裂液挂的状态标签(fg.TbStatusTag.id:Acid/Frozen/Oil);none=不挂</t>
+        </is>
+      </c>
+      <c r="BE3" t="inlineStr">
+        <is>
+          <t>上面那个状态标签的持续秒数</t>
+        </is>
+      </c>
+      <c r="BF3" t="inlineStr">
+        <is>
+          <t>自爆单位被火击毁时的爆燃伤害倍率;0=不爆燃</t>
+        </is>
+      </c>
+      <c r="BG3" t="inlineStr">
+        <is>
+          <t>被击毁后分裂成几滩会爬行的腐蚀液(整数,≤8);0=不分裂</t>
+        </is>
+      </c>
+      <c r="BH3" t="inlineStr">
+        <is>
+          <t>每滩分裂液的耐久</t>
+        </is>
+      </c>
+      <c r="BI3" t="inlineStr">
+        <is>
+          <t>分裂液爬行速度(米/秒)</t>
+        </is>
+      </c>
+      <c r="BJ3" t="inlineStr">
+        <is>
+          <t>分裂液多久蒸发(秒)</t>
+        </is>
+      </c>
+      <c r="BK3" t="inlineStr">
+        <is>
+          <t>分裂液接触时每秒伤害(多滩同时接触不叠加;难度倍率另乘)</t>
+        </is>
+      </c>
+      <c r="BL3" t="inlineStr">
         <is>
           <t>FG9-UX-01 图鉴互链:逗号分隔的图鉴条目ID(reaction:/comp:/fw:/enemy:/codex.*),敌人 ↔ 弱点相关的反应 / 组件 / 机制;none=只链阵营</t>
         </is>
@@ -1372,7 +1567,48 @@
       <c r="AX4" t="n">
         <v>0</v>
       </c>
-      <c r="AY4" t="inlineStr">
+      <c r="AY4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ4" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA4" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB4" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC4" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD4" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="BE4" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF4" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG4" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH4" t="n">
+        <v>0</v>
+      </c>
+      <c r="BI4" t="n">
+        <v>0</v>
+      </c>
+      <c r="BJ4" t="n">
+        <v>0</v>
+      </c>
+      <c r="BK4" t="n">
+        <v>0</v>
+      </c>
+      <c r="BL4" t="inlineStr">
         <is>
           <t>comp:comp_gun</t>
         </is>
@@ -1563,7 +1799,48 @@
       <c r="AX5" t="n">
         <v>0</v>
       </c>
-      <c r="AY5" t="inlineStr">
+      <c r="AY5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ5" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA5" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB5" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC5" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD5" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="BE5" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF5" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG5" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH5" t="n">
+        <v>0</v>
+      </c>
+      <c r="BI5" t="n">
+        <v>0</v>
+      </c>
+      <c r="BJ5" t="n">
+        <v>0</v>
+      </c>
+      <c r="BK5" t="n">
+        <v>0</v>
+      </c>
+      <c r="BL5" t="inlineStr">
         <is>
           <t>comp:comp_gun,codex.signal.exposure</t>
         </is>
@@ -1754,7 +2031,48 @@
       <c r="AX6" t="n">
         <v>0</v>
       </c>
-      <c r="AY6" t="inlineStr">
+      <c r="AY6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ6" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA6" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB6" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC6" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD6" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="BE6" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF6" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG6" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH6" t="n">
+        <v>0</v>
+      </c>
+      <c r="BI6" t="n">
+        <v>0</v>
+      </c>
+      <c r="BJ6" t="n">
+        <v>0</v>
+      </c>
+      <c r="BK6" t="n">
+        <v>0</v>
+      </c>
+      <c r="BL6" t="inlineStr">
         <is>
           <t>comp:comp_cannon</t>
         </is>
@@ -1945,7 +2263,48 @@
       <c r="AX7" t="n">
         <v>0</v>
       </c>
-      <c r="AY7" t="inlineStr">
+      <c r="AY7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ7" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA7" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB7" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC7" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD7" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="BE7" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF7" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG7" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH7" t="n">
+        <v>0</v>
+      </c>
+      <c r="BI7" t="n">
+        <v>0</v>
+      </c>
+      <c r="BJ7" t="n">
+        <v>0</v>
+      </c>
+      <c r="BK7" t="n">
+        <v>0</v>
+      </c>
+      <c r="BL7" t="inlineStr">
         <is>
           <t>reaction:reaction_meltoverload</t>
         </is>
@@ -2136,7 +2495,48 @@
       <c r="AX8" t="n">
         <v>0</v>
       </c>
-      <c r="AY8" t="inlineStr">
+      <c r="AY8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ8" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA8" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB8" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC8" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD8" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="BE8" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF8" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG8" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH8" t="n">
+        <v>0</v>
+      </c>
+      <c r="BI8" t="n">
+        <v>0</v>
+      </c>
+      <c r="BJ8" t="n">
+        <v>0</v>
+      </c>
+      <c r="BK8" t="n">
+        <v>0</v>
+      </c>
+      <c r="BL8" t="inlineStr">
         <is>
           <t>enemy:enemy_armorbot</t>
         </is>
@@ -2327,7 +2727,48 @@
       <c r="AX9" t="n">
         <v>0</v>
       </c>
-      <c r="AY9" t="inlineStr">
+      <c r="AY9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ9" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA9" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB9" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC9" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD9" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="BE9" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF9" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG9" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH9" t="n">
+        <v>0</v>
+      </c>
+      <c r="BI9" t="n">
+        <v>0</v>
+      </c>
+      <c r="BJ9" t="n">
+        <v>0</v>
+      </c>
+      <c r="BK9" t="n">
+        <v>0</v>
+      </c>
+      <c r="BL9" t="inlineStr">
         <is>
           <t>enemy:enemy_core_node,codex.intel.boss_weakness</t>
         </is>
@@ -2518,7 +2959,48 @@
       <c r="AX10" t="n">
         <v>0</v>
       </c>
-      <c r="AY10" t="inlineStr">
+      <c r="AY10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ10" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA10" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB10" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC10" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD10" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="BE10" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF10" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG10" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH10" t="n">
+        <v>0</v>
+      </c>
+      <c r="BI10" t="n">
+        <v>0</v>
+      </c>
+      <c r="BJ10" t="n">
+        <v>0</v>
+      </c>
+      <c r="BK10" t="n">
+        <v>0</v>
+      </c>
+      <c r="BL10" t="inlineStr">
         <is>
           <t>enemy:enemy_core_boss</t>
         </is>
@@ -2709,7 +3191,48 @@
       <c r="AX11" t="n">
         <v>0</v>
       </c>
-      <c r="AY11" t="inlineStr">
+      <c r="AY11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ11" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA11" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB11" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC11" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD11" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="BE11" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF11" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG11" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH11" t="n">
+        <v>0</v>
+      </c>
+      <c r="BI11" t="n">
+        <v>0</v>
+      </c>
+      <c r="BJ11" t="n">
+        <v>0</v>
+      </c>
+      <c r="BK11" t="n">
+        <v>0</v>
+      </c>
+      <c r="BL11" t="inlineStr">
         <is>
           <t>codex.signal.exposure,codex.signal.core_firmware</t>
         </is>
@@ -2900,7 +3423,48 @@
       <c r="AX12" t="n">
         <v>0</v>
       </c>
-      <c r="AY12" t="inlineStr">
+      <c r="AY12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ12" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA12" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB12" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC12" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD12" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="BE12" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF12" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG12" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH12" t="n">
+        <v>0</v>
+      </c>
+      <c r="BI12" t="n">
+        <v>0</v>
+      </c>
+      <c r="BJ12" t="n">
+        <v>0</v>
+      </c>
+      <c r="BK12" t="n">
+        <v>0</v>
+      </c>
+      <c r="BL12" t="inlineStr">
         <is>
           <t>comp:comp_ram</t>
         </is>
@@ -3091,7 +3655,48 @@
       <c r="AX13" t="n">
         <v>0</v>
       </c>
-      <c r="AY13" t="inlineStr">
+      <c r="AY13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ13" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA13" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB13" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC13" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD13" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="BE13" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF13" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG13" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH13" t="n">
+        <v>0</v>
+      </c>
+      <c r="BI13" t="n">
+        <v>0</v>
+      </c>
+      <c r="BJ13" t="n">
+        <v>0</v>
+      </c>
+      <c r="BK13" t="n">
+        <v>0</v>
+      </c>
+      <c r="BL13" t="inlineStr">
         <is>
           <t>comp:func_marker,comp:struct_relay</t>
         </is>
@@ -3282,7 +3887,48 @@
       <c r="AX14" t="n">
         <v>0</v>
       </c>
-      <c r="AY14" t="inlineStr">
+      <c r="AY14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ14" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA14" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB14" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC14" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD14" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="BE14" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF14" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG14" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH14" t="n">
+        <v>0</v>
+      </c>
+      <c r="BI14" t="n">
+        <v>0</v>
+      </c>
+      <c r="BJ14" t="n">
+        <v>0</v>
+      </c>
+      <c r="BK14" t="n">
+        <v>0</v>
+      </c>
+      <c r="BL14" t="inlineStr">
         <is>
           <t>codex.intel.listening_post</t>
         </is>
@@ -3473,7 +4119,48 @@
       <c r="AX15" t="n">
         <v>0</v>
       </c>
-      <c r="AY15" t="inlineStr">
+      <c r="AY15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ15" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA15" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB15" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC15" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD15" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="BE15" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF15" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG15" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH15" t="n">
+        <v>0</v>
+      </c>
+      <c r="BI15" t="n">
+        <v>0</v>
+      </c>
+      <c r="BJ15" t="n">
+        <v>0</v>
+      </c>
+      <c r="BK15" t="n">
+        <v>0</v>
+      </c>
+      <c r="BL15" t="inlineStr">
         <is>
           <t>codex.signal.uplink</t>
         </is>
@@ -3664,7 +4351,48 @@
       <c r="AX16" t="n">
         <v>0</v>
       </c>
-      <c r="AY16" t="inlineStr">
+      <c r="AY16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ16" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA16" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB16" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC16" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD16" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="BE16" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF16" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG16" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH16" t="n">
+        <v>0</v>
+      </c>
+      <c r="BI16" t="n">
+        <v>0</v>
+      </c>
+      <c r="BJ16" t="n">
+        <v>0</v>
+      </c>
+      <c r="BK16" t="n">
+        <v>0</v>
+      </c>
+      <c r="BL16" t="inlineStr">
         <is>
           <t>enemy:enemy_mind_relay,comp:func_marker,codex.intel.listening_post</t>
         </is>
@@ -3855,7 +4583,48 @@
       <c r="AX17" t="n">
         <v>0</v>
       </c>
-      <c r="AY17" t="inlineStr">
+      <c r="AY17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ17" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA17" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB17" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC17" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD17" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="BE17" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF17" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG17" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH17" t="n">
+        <v>0</v>
+      </c>
+      <c r="BI17" t="n">
+        <v>0</v>
+      </c>
+      <c r="BJ17" t="n">
+        <v>0</v>
+      </c>
+      <c r="BK17" t="n">
+        <v>0</v>
+      </c>
+      <c r="BL17" t="inlineStr">
         <is>
           <t>enemy:enemy_mind_core,comp:func_marker</t>
         </is>
@@ -4046,7 +4815,48 @@
       <c r="AX18" t="n">
         <v>0</v>
       </c>
-      <c r="AY18" t="inlineStr">
+      <c r="AY18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ18" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA18" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB18" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC18" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD18" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="BE18" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF18" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG18" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH18" t="n">
+        <v>0</v>
+      </c>
+      <c r="BI18" t="n">
+        <v>0</v>
+      </c>
+      <c r="BJ18" t="n">
+        <v>0</v>
+      </c>
+      <c r="BK18" t="n">
+        <v>0</v>
+      </c>
+      <c r="BL18" t="inlineStr">
         <is>
           <t>comp:comp_gun</t>
         </is>
@@ -4237,7 +5047,48 @@
       <c r="AX19" t="n">
         <v>4</v>
       </c>
-      <c r="AY19" t="inlineStr">
+      <c r="AY19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ19" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA19" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB19" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC19" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD19" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="BE19" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF19" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG19" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH19" t="n">
+        <v>0</v>
+      </c>
+      <c r="BI19" t="n">
+        <v>0</v>
+      </c>
+      <c r="BJ19" t="n">
+        <v>0</v>
+      </c>
+      <c r="BK19" t="n">
+        <v>0</v>
+      </c>
+      <c r="BL19" t="inlineStr">
         <is>
           <t>comp:comp_gun</t>
         </is>
@@ -4428,7 +5279,48 @@
       <c r="AX20" t="n">
         <v>0</v>
       </c>
-      <c r="AY20" t="inlineStr">
+      <c r="AY20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ20" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA20" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB20" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC20" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD20" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="BE20" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF20" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG20" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH20" t="n">
+        <v>0</v>
+      </c>
+      <c r="BI20" t="n">
+        <v>0</v>
+      </c>
+      <c r="BJ20" t="n">
+        <v>0</v>
+      </c>
+      <c r="BK20" t="n">
+        <v>0</v>
+      </c>
+      <c r="BL20" t="inlineStr">
         <is>
           <t>codex.expedition.drop</t>
         </is>
@@ -4619,7 +5511,48 @@
       <c r="AX21" t="n">
         <v>0</v>
       </c>
-      <c r="AY21" t="inlineStr">
+      <c r="AY21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ21" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA21" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB21" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC21" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD21" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="BE21" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF21" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG21" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH21" t="n">
+        <v>0</v>
+      </c>
+      <c r="BI21" t="n">
+        <v>0</v>
+      </c>
+      <c r="BJ21" t="n">
+        <v>0</v>
+      </c>
+      <c r="BK21" t="n">
+        <v>0</v>
+      </c>
+      <c r="BL21" t="inlineStr">
         <is>
           <t>enemy:enemy_airburst,enemy:enemy_strider</t>
         </is>
@@ -4810,9 +5743,1442 @@
       <c r="AX22" t="n">
         <v>0</v>
       </c>
-      <c r="AY22" t="inlineStr">
+      <c r="AY22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ22" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA22" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB22" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC22" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD22" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="BE22" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF22" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG22" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH22" t="n">
+        <v>0</v>
+      </c>
+      <c r="BI22" t="n">
+        <v>0</v>
+      </c>
+      <c r="BJ22" t="n">
+        <v>0</v>
+      </c>
+      <c r="BK22" t="n">
+        <v>0</v>
+      </c>
+      <c r="BL22" t="inlineStr">
         <is>
           <t>reaction:reaction_meltoverload</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr"/>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>enemy_sprayer</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>enemy.sprayer.name</t>
+        </is>
+      </c>
+      <c r="D23" t="n">
+        <v>200</v>
+      </c>
+      <c r="E23" t="n">
+        <v>0</v>
+      </c>
+      <c r="F23" t="n">
+        <v>25</v>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>clarity</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>control</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>spray</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>acid_proof,adapt_insulate</t>
+        </is>
+      </c>
+      <c r="L23" t="n">
+        <v>2</v>
+      </c>
+      <c r="M23" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="N23" t="n">
+        <v>9</v>
+      </c>
+      <c r="O23" t="n">
+        <v>6</v>
+      </c>
+      <c r="P23" t="n">
+        <v>6</v>
+      </c>
+      <c r="Q23" t="n">
+        <v>0</v>
+      </c>
+      <c r="R23" t="n">
+        <v>16</v>
+      </c>
+      <c r="S23" t="n">
+        <v>0</v>
+      </c>
+      <c r="T23" t="n">
+        <v>0</v>
+      </c>
+      <c r="U23" t="n">
+        <v>0</v>
+      </c>
+      <c r="V23" t="n">
+        <v>0</v>
+      </c>
+      <c r="W23" t="n">
+        <v>0</v>
+      </c>
+      <c r="X23" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y23" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA23" t="n">
+        <v>90</v>
+      </c>
+      <c r="AB23" t="inlineStr">
+        <is>
+          <t>enemy.sprayer.desc</t>
+        </is>
+      </c>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>enemy.sprayer.weakness</t>
+        </is>
+      </c>
+      <c r="AD23" t="inlineStr">
+        <is>
+          <t>enemy.sprayer.trait</t>
+        </is>
+      </c>
+      <c r="AE23" t="inlineStr">
+        <is>
+          <t>comp_sprayer,fw_acid</t>
+        </is>
+      </c>
+      <c r="AF23" t="inlineStr">
+        <is>
+          <t>minion</t>
+        </is>
+      </c>
+      <c r="AG23" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="AH23" t="n">
+        <v>30</v>
+      </c>
+      <c r="AI23" t="inlineStr">
+        <is>
+          <t>icon_enemy_jammer</t>
+        </is>
+      </c>
+      <c r="AJ23" t="inlineStr">
+        <is>
+          <t>clarity_sprayer</t>
+        </is>
+      </c>
+      <c r="AK23" t="inlineStr">
+        <is>
+          <t>#8FBF3A</t>
+        </is>
+      </c>
+      <c r="AL23" t="inlineStr">
+        <is>
+          <t>sfx_signal_jam</t>
+        </is>
+      </c>
+      <c r="AM23" t="inlineStr">
+        <is>
+          <t>vfx_jam_field_placeholder</t>
+        </is>
+      </c>
+      <c r="AN23" t="n">
+        <v>1</v>
+      </c>
+      <c r="AO23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY23" t="n">
+        <v>30</v>
+      </c>
+      <c r="AZ23" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="BA23" t="n">
+        <v>8</v>
+      </c>
+      <c r="BB23" t="n">
+        <v>6</v>
+      </c>
+      <c r="BC23" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD23" t="inlineStr">
+        <is>
+          <t>Acid</t>
+        </is>
+      </c>
+      <c r="BE23" t="n">
+        <v>4</v>
+      </c>
+      <c r="BF23" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG23" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH23" t="n">
+        <v>0</v>
+      </c>
+      <c r="BI23" t="n">
+        <v>0</v>
+      </c>
+      <c r="BJ23" t="n">
+        <v>0</v>
+      </c>
+      <c r="BK23" t="n">
+        <v>0</v>
+      </c>
+      <c r="BL23" t="inlineStr">
+        <is>
+          <t>fw:fw_coolant,codex.clarity.spray,codex.clarity.acid</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr"/>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>enemy_oil_crawler</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>enemy.oil_crawler.name</t>
+        </is>
+      </c>
+      <c r="D24" t="n">
+        <v>60</v>
+      </c>
+      <c r="E24" t="n">
+        <v>0</v>
+      </c>
+      <c r="F24" t="n">
+        <v>10</v>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>clarity</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>suicide</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>crawl_burst</t>
+        </is>
+      </c>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>acid_proof</t>
+        </is>
+      </c>
+      <c r="L24" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="M24" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="N24" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="O24" t="n">
+        <v>40</v>
+      </c>
+      <c r="P24" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q24" t="n">
+        <v>0</v>
+      </c>
+      <c r="R24" t="n">
+        <v>16</v>
+      </c>
+      <c r="S24" t="n">
+        <v>1</v>
+      </c>
+      <c r="T24" t="n">
+        <v>12</v>
+      </c>
+      <c r="U24" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="V24" t="n">
+        <v>0</v>
+      </c>
+      <c r="W24" t="n">
+        <v>0</v>
+      </c>
+      <c r="X24" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y24" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA24" t="n">
+        <v>90</v>
+      </c>
+      <c r="AB24" t="inlineStr">
+        <is>
+          <t>enemy.oil_crawler.desc</t>
+        </is>
+      </c>
+      <c r="AC24" t="inlineStr">
+        <is>
+          <t>enemy.oil_crawler.weakness</t>
+        </is>
+      </c>
+      <c r="AD24" t="inlineStr">
+        <is>
+          <t>enemy.oil_crawler.trait</t>
+        </is>
+      </c>
+      <c r="AE24" t="inlineStr">
+        <is>
+          <t>comp_claw,fw_oilleak</t>
+        </is>
+      </c>
+      <c r="AF24" t="inlineStr">
+        <is>
+          <t>minion</t>
+        </is>
+      </c>
+      <c r="AG24" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="AH24" t="n">
+        <v>12</v>
+      </c>
+      <c r="AI24" t="inlineStr">
+        <is>
+          <t>icon_enemy_scout</t>
+        </is>
+      </c>
+      <c r="AJ24" t="inlineStr">
+        <is>
+          <t>clarity_crawler</t>
+        </is>
+      </c>
+      <c r="AK24" t="inlineStr">
+        <is>
+          <t>#3B3A2E</t>
+        </is>
+      </c>
+      <c r="AL24" t="inlineStr">
+        <is>
+          <t>sfx_enemy_fire</t>
+        </is>
+      </c>
+      <c r="AM24" t="inlineStr">
+        <is>
+          <t>vfx_none_placeholder</t>
+        </is>
+      </c>
+      <c r="AN24" t="n">
+        <v>1</v>
+      </c>
+      <c r="AO24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ24" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="BA24" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB24" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC24" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD24" t="inlineStr">
+        <is>
+          <t>Oil</t>
+        </is>
+      </c>
+      <c r="BE24" t="n">
+        <v>10</v>
+      </c>
+      <c r="BF24" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="BG24" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH24" t="n">
+        <v>0</v>
+      </c>
+      <c r="BI24" t="n">
+        <v>0</v>
+      </c>
+      <c r="BJ24" t="n">
+        <v>0</v>
+      </c>
+      <c r="BK24" t="n">
+        <v>0</v>
+      </c>
+      <c r="BL24" t="inlineStr">
+        <is>
+          <t>reaction:reaction_deflagrate,fw:fw_burntrail,codex.clarity.crawler</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr"/>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>enemy_ln2_pump</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>enemy.ln2_pump.name</t>
+        </is>
+      </c>
+      <c r="D25" t="n">
+        <v>240</v>
+      </c>
+      <c r="E25" t="n">
+        <v>0</v>
+      </c>
+      <c r="F25" t="n">
+        <v>30</v>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>clarity</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>disabler</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>spray</t>
+        </is>
+      </c>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>acid_proof,adapt_insulate</t>
+        </is>
+      </c>
+      <c r="L25" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="M25" t="n">
+        <v>1</v>
+      </c>
+      <c r="N25" t="n">
+        <v>8</v>
+      </c>
+      <c r="O25" t="n">
+        <v>3</v>
+      </c>
+      <c r="P25" t="n">
+        <v>7</v>
+      </c>
+      <c r="Q25" t="n">
+        <v>0</v>
+      </c>
+      <c r="R25" t="n">
+        <v>14</v>
+      </c>
+      <c r="S25" t="n">
+        <v>0</v>
+      </c>
+      <c r="T25" t="n">
+        <v>0</v>
+      </c>
+      <c r="U25" t="n">
+        <v>0</v>
+      </c>
+      <c r="V25" t="n">
+        <v>0</v>
+      </c>
+      <c r="W25" t="n">
+        <v>0</v>
+      </c>
+      <c r="X25" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y25" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA25" t="n">
+        <v>90</v>
+      </c>
+      <c r="AB25" t="inlineStr">
+        <is>
+          <t>enemy.ln2_pump.desc</t>
+        </is>
+      </c>
+      <c r="AC25" t="inlineStr">
+        <is>
+          <t>enemy.ln2_pump.weakness</t>
+        </is>
+      </c>
+      <c r="AD25" t="inlineStr">
+        <is>
+          <t>enemy.ln2_pump.trait</t>
+        </is>
+      </c>
+      <c r="AE25" t="inlineStr">
+        <is>
+          <t>comp_sprayer,fw_nitrogen</t>
+        </is>
+      </c>
+      <c r="AF25" t="inlineStr">
+        <is>
+          <t>minion</t>
+        </is>
+      </c>
+      <c r="AG25" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="AH25" t="n">
+        <v>35</v>
+      </c>
+      <c r="AI25" t="inlineStr">
+        <is>
+          <t>icon_enemy_jammer</t>
+        </is>
+      </c>
+      <c r="AJ25" t="inlineStr">
+        <is>
+          <t>clarity_pump</t>
+        </is>
+      </c>
+      <c r="AK25" t="inlineStr">
+        <is>
+          <t>#6FC6E0</t>
+        </is>
+      </c>
+      <c r="AL25" t="inlineStr">
+        <is>
+          <t>sfx_signal_jam</t>
+        </is>
+      </c>
+      <c r="AM25" t="inlineStr">
+        <is>
+          <t>vfx_jam_field_placeholder</t>
+        </is>
+      </c>
+      <c r="AN25" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="AO25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY25" t="n">
+        <v>28</v>
+      </c>
+      <c r="AZ25" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="BA25" t="n">
+        <v>6</v>
+      </c>
+      <c r="BB25" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC25" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="BD25" t="inlineStr">
+        <is>
+          <t>Frozen</t>
+        </is>
+      </c>
+      <c r="BE25" t="n">
+        <v>4</v>
+      </c>
+      <c r="BF25" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG25" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH25" t="n">
+        <v>0</v>
+      </c>
+      <c r="BI25" t="n">
+        <v>0</v>
+      </c>
+      <c r="BJ25" t="n">
+        <v>0</v>
+      </c>
+      <c r="BK25" t="n">
+        <v>0</v>
+      </c>
+      <c r="BL25" t="inlineStr">
+        <is>
+          <t>codex.clarity.chill,reaction:reaction_thermalshock,fw:fw_burntrail</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr"/>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>enemy_deact_drone</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>enemy.deact_drone.name</t>
+        </is>
+      </c>
+      <c r="D26" t="n">
+        <v>70</v>
+      </c>
+      <c r="E26" t="n">
+        <v>0</v>
+      </c>
+      <c r="F26" t="n">
+        <v>15</v>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>clarity</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>saboteur</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>pollute</t>
+        </is>
+      </c>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>acid_proof,airborne,assembled</t>
+        </is>
+      </c>
+      <c r="L26" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="M26" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="N26" t="n">
+        <v>7</v>
+      </c>
+      <c r="O26" t="n">
+        <v>5</v>
+      </c>
+      <c r="P26" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="Q26" t="n">
+        <v>0</v>
+      </c>
+      <c r="R26" t="n">
+        <v>16</v>
+      </c>
+      <c r="S26" t="n">
+        <v>0</v>
+      </c>
+      <c r="T26" t="n">
+        <v>0</v>
+      </c>
+      <c r="U26" t="n">
+        <v>4</v>
+      </c>
+      <c r="V26" t="n">
+        <v>0</v>
+      </c>
+      <c r="W26" t="n">
+        <v>0</v>
+      </c>
+      <c r="X26" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y26" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA26" t="n">
+        <v>90</v>
+      </c>
+      <c r="AB26" t="inlineStr">
+        <is>
+          <t>enemy.deact_drone.desc</t>
+        </is>
+      </c>
+      <c r="AC26" t="inlineStr">
+        <is>
+          <t>enemy.deact_drone.weakness</t>
+        </is>
+      </c>
+      <c r="AD26" t="inlineStr">
+        <is>
+          <t>enemy.deact_drone.trait</t>
+        </is>
+      </c>
+      <c r="AE26" t="inlineStr">
+        <is>
+          <t>comp_gun,fw_acid</t>
+        </is>
+      </c>
+      <c r="AF26" t="inlineStr">
+        <is>
+          <t>minion</t>
+        </is>
+      </c>
+      <c r="AG26" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="AH26" t="n">
+        <v>20</v>
+      </c>
+      <c r="AI26" t="inlineStr">
+        <is>
+          <t>icon_enemy_scout</t>
+        </is>
+      </c>
+      <c r="AJ26" t="inlineStr">
+        <is>
+          <t>clarity_drone</t>
+        </is>
+      </c>
+      <c r="AK26" t="inlineStr">
+        <is>
+          <t>#C9E07A</t>
+        </is>
+      </c>
+      <c r="AL26" t="inlineStr">
+        <is>
+          <t>sfx_enemy_fire</t>
+        </is>
+      </c>
+      <c r="AM26" t="inlineStr">
+        <is>
+          <t>vfx_none_placeholder</t>
+        </is>
+      </c>
+      <c r="AN26" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AO26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ26" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA26" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB26" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC26" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD26" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="BE26" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF26" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG26" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH26" t="n">
+        <v>0</v>
+      </c>
+      <c r="BI26" t="n">
+        <v>0</v>
+      </c>
+      <c r="BJ26" t="n">
+        <v>0</v>
+      </c>
+      <c r="BK26" t="n">
+        <v>0</v>
+      </c>
+      <c r="BL26" t="inlineStr">
+        <is>
+          <t>comp:comp_gun,codex.clarity.air</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr"/>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>enemy_corrosion_swarm</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>enemy.corrosion_swarm.name</t>
+        </is>
+      </c>
+      <c r="D27" t="n">
+        <v>25</v>
+      </c>
+      <c r="E27" t="n">
+        <v>0</v>
+      </c>
+      <c r="F27" t="n">
+        <v>4</v>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>clarity</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>swarm</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>swarm</t>
+        </is>
+      </c>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>acid_proof,anti_building,assembled</t>
+        </is>
+      </c>
+      <c r="L27" t="n">
+        <v>4</v>
+      </c>
+      <c r="M27" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="N27" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="O27" t="n">
+        <v>3</v>
+      </c>
+      <c r="P27" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="Q27" t="n">
+        <v>0</v>
+      </c>
+      <c r="R27" t="n">
+        <v>12</v>
+      </c>
+      <c r="S27" t="n">
+        <v>0</v>
+      </c>
+      <c r="T27" t="n">
+        <v>0</v>
+      </c>
+      <c r="U27" t="n">
+        <v>0</v>
+      </c>
+      <c r="V27" t="n">
+        <v>0</v>
+      </c>
+      <c r="W27" t="n">
+        <v>0</v>
+      </c>
+      <c r="X27" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y27" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA27" t="n">
+        <v>90</v>
+      </c>
+      <c r="AB27" t="inlineStr">
+        <is>
+          <t>enemy.corrosion_swarm.desc</t>
+        </is>
+      </c>
+      <c r="AC27" t="inlineStr">
+        <is>
+          <t>enemy.corrosion_swarm.weakness</t>
+        </is>
+      </c>
+      <c r="AD27" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="AE27" t="inlineStr">
+        <is>
+          <t>comp_shovel,fw_acid</t>
+        </is>
+      </c>
+      <c r="AF27" t="inlineStr">
+        <is>
+          <t>minion</t>
+        </is>
+      </c>
+      <c r="AG27" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="AH27" t="n">
+        <v>4</v>
+      </c>
+      <c r="AI27" t="inlineStr">
+        <is>
+          <t>icon_enemy_scout</t>
+        </is>
+      </c>
+      <c r="AJ27" t="inlineStr">
+        <is>
+          <t>clarity_swarm</t>
+        </is>
+      </c>
+      <c r="AK27" t="inlineStr">
+        <is>
+          <t>#A6D94A</t>
+        </is>
+      </c>
+      <c r="AL27" t="inlineStr">
+        <is>
+          <t>sfx_enemy_fire</t>
+        </is>
+      </c>
+      <c r="AM27" t="inlineStr">
+        <is>
+          <t>vfx_none_placeholder</t>
+        </is>
+      </c>
+      <c r="AN27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ27" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA27" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB27" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC27" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD27" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="BE27" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF27" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG27" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH27" t="n">
+        <v>0</v>
+      </c>
+      <c r="BI27" t="n">
+        <v>0</v>
+      </c>
+      <c r="BJ27" t="n">
+        <v>0</v>
+      </c>
+      <c r="BK27" t="n">
+        <v>0</v>
+      </c>
+      <c r="BL27" t="inlineStr">
+        <is>
+          <t>fw:fw_shockwave,fw:fw_cluster</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr"/>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>enemy_settling_tank</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>enemy.settling_tank.name</t>
+        </is>
+      </c>
+      <c r="D28" t="n">
+        <v>900</v>
+      </c>
+      <c r="E28" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="F28" t="n">
+        <v>60</v>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>clarity</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>control</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>elite</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>pivot</t>
+        </is>
+      </c>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>acid_proof,adapt_insulate</t>
+        </is>
+      </c>
+      <c r="L28" t="n">
+        <v>1</v>
+      </c>
+      <c r="M28" t="n">
+        <v>2</v>
+      </c>
+      <c r="N28" t="n">
+        <v>6</v>
+      </c>
+      <c r="O28" t="n">
+        <v>1</v>
+      </c>
+      <c r="P28" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q28" t="n">
+        <v>0</v>
+      </c>
+      <c r="R28" t="n">
+        <v>16</v>
+      </c>
+      <c r="S28" t="n">
+        <v>0</v>
+      </c>
+      <c r="T28" t="n">
+        <v>0</v>
+      </c>
+      <c r="U28" t="n">
+        <v>6</v>
+      </c>
+      <c r="V28" t="n">
+        <v>18</v>
+      </c>
+      <c r="W28" t="n">
+        <v>0</v>
+      </c>
+      <c r="X28" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y28" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA28" t="n">
+        <v>90</v>
+      </c>
+      <c r="AB28" t="inlineStr">
+        <is>
+          <t>enemy.settling_tank.desc</t>
+        </is>
+      </c>
+      <c r="AC28" t="inlineStr">
+        <is>
+          <t>enemy.settling_tank.weakness</t>
+        </is>
+      </c>
+      <c r="AD28" t="inlineStr">
+        <is>
+          <t>enemy.settling_tank.trait</t>
+        </is>
+      </c>
+      <c r="AE28" t="inlineStr">
+        <is>
+          <t>comp_sprayer,fw_acid</t>
+        </is>
+      </c>
+      <c r="AF28" t="inlineStr">
+        <is>
+          <t>elite</t>
+        </is>
+      </c>
+      <c r="AG28" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="AH28" t="n">
+        <v>120</v>
+      </c>
+      <c r="AI28" t="inlineStr">
+        <is>
+          <t>icon_enemy_armorbot</t>
+        </is>
+      </c>
+      <c r="AJ28" t="inlineStr">
+        <is>
+          <t>clarity_tank</t>
+        </is>
+      </c>
+      <c r="AK28" t="inlineStr">
+        <is>
+          <t>#7FA83A</t>
+        </is>
+      </c>
+      <c r="AL28" t="inlineStr">
+        <is>
+          <t>sfx_enemy_fire_heavy</t>
+        </is>
+      </c>
+      <c r="AM28" t="inlineStr">
+        <is>
+          <t>vfx_boss_phase_placeholder</t>
+        </is>
+      </c>
+      <c r="AN28" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="AO28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW28" t="n">
+        <v>70</v>
+      </c>
+      <c r="AX28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY28" t="n">
+        <v>18</v>
+      </c>
+      <c r="AZ28" t="n">
+        <v>1</v>
+      </c>
+      <c r="BA28" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB28" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC28" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD28" t="inlineStr">
+        <is>
+          <t>Acid</t>
+        </is>
+      </c>
+      <c r="BE28" t="n">
+        <v>4</v>
+      </c>
+      <c r="BF28" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG28" t="n">
+        <v>3</v>
+      </c>
+      <c r="BH28" t="n">
+        <v>60</v>
+      </c>
+      <c r="BI28" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="BJ28" t="n">
+        <v>20</v>
+      </c>
+      <c r="BK28" t="n">
+        <v>8</v>
+      </c>
+      <c r="BL28" t="inlineStr">
+        <is>
+          <t>codex.clarity.pivot,enemy:enemy_sprayer</t>
         </is>
       </c>
     </row>

--- a/Configs/GameConfig/Datas/fg/#MechEnemy-机械敌人.xlsx
+++ b/Configs/GameConfig/Datas/fg/#MechEnemy-机械敌人.xlsx
@@ -6452,7 +6452,7 @@
         <v>0</v>
       </c>
       <c r="BC25" t="n">
-        <v>0.5</v>
+        <v>0.6</v>
       </c>
       <c r="BD25" t="inlineStr">
         <is>

--- a/Configs/GameConfig/Datas/fg/#MechEnemy-机械敌人.xlsx
+++ b/Configs/GameConfig/Datas/fg/#MechEnemy-机械敌人.xlsx
@@ -1343,7 +1343,7 @@
       </c>
       <c r="BE3" t="inlineStr">
         <is>
-          <t>上面那个状态标签的持续秒数</t>
+          <t>上面那个状态标签的持续秒数(喷淋 / 喷灌命中与池子;自爆单位 = 油迹与溅油挂油的秒数)</t>
         </is>
       </c>
       <c r="BF3" t="inlineStr">
@@ -1358,7 +1358,7 @@
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>每滩分裂液的耐久</t>
+          <t>每滩分裂液的耐久(难度 / 精英耐久倍率另乘,与本体同一口径)</t>
         </is>
       </c>
       <c r="BI3" t="inlineStr">

--- a/Configs/GameConfig/Datas/fg/#MechEnemy-机械敌人.xlsx
+++ b/Configs/GameConfig/Datas/fg/#MechEnemy-机械敌人.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BL28"/>
+  <dimension ref="A1:BL32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -7179,6 +7179,934 @@
       <c r="BL28" t="inlineStr">
         <is>
           <t>codex.clarity.pivot,enemy:enemy_sprayer</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr"/>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>enemy_baptism_tower</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>enemy.baptism_tower.name</t>
+        </is>
+      </c>
+      <c r="D29" t="n">
+        <v>2400</v>
+      </c>
+      <c r="E29" t="n">
+        <v>0</v>
+      </c>
+      <c r="F29" t="n">
+        <v>0</v>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>clarity</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>boss</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>boss</t>
+        </is>
+      </c>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>ring_spray</t>
+        </is>
+      </c>
+      <c r="K29" t="inlineStr">
+        <is>
+          <t>external_health,acid_proof</t>
+        </is>
+      </c>
+      <c r="L29" t="n">
+        <v>0</v>
+      </c>
+      <c r="M29" t="n">
+        <v>4</v>
+      </c>
+      <c r="N29" t="n">
+        <v>0</v>
+      </c>
+      <c r="O29" t="n">
+        <v>0</v>
+      </c>
+      <c r="P29" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q29" t="n">
+        <v>0</v>
+      </c>
+      <c r="R29" t="n">
+        <v>0</v>
+      </c>
+      <c r="S29" t="n">
+        <v>0</v>
+      </c>
+      <c r="T29" t="n">
+        <v>0</v>
+      </c>
+      <c r="U29" t="n">
+        <v>16</v>
+      </c>
+      <c r="V29" t="n">
+        <v>14</v>
+      </c>
+      <c r="W29" t="n">
+        <v>0</v>
+      </c>
+      <c r="X29" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y29" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z29" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA29" t="n">
+        <v>90</v>
+      </c>
+      <c r="AB29" t="inlineStr">
+        <is>
+          <t>enemy.baptism_tower.desc</t>
+        </is>
+      </c>
+      <c r="AC29" t="inlineStr">
+        <is>
+          <t>enemy.baptism_tower.weakness</t>
+        </is>
+      </c>
+      <c r="AD29" t="inlineStr">
+        <is>
+          <t>enemy.baptism_tower.trait</t>
+        </is>
+      </c>
+      <c r="AE29" t="inlineStr">
+        <is>
+          <t>fw_amplify,fw_acid</t>
+        </is>
+      </c>
+      <c r="AF29" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="AG29" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="AH29" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI29" t="inlineStr">
+        <is>
+          <t>icon_enemy_core_boss</t>
+        </is>
+      </c>
+      <c r="AJ29" t="inlineStr">
+        <is>
+          <t>clarity_tank</t>
+        </is>
+      </c>
+      <c r="AK29" t="inlineStr">
+        <is>
+          <t>#3E8A72</t>
+        </is>
+      </c>
+      <c r="AL29" t="inlineStr">
+        <is>
+          <t>sfx_boss_phase</t>
+        </is>
+      </c>
+      <c r="AM29" t="inlineStr">
+        <is>
+          <t>vfx_boss_phase_placeholder</t>
+        </is>
+      </c>
+      <c r="AN29" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AO29" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP29" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ29" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR29" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS29" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT29" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU29" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV29" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW29" t="n">
+        <v>40</v>
+      </c>
+      <c r="AX29" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY29" t="n">
+        <v>20</v>
+      </c>
+      <c r="AZ29" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA29" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB29" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC29" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD29" t="inlineStr">
+        <is>
+          <t>Acid</t>
+        </is>
+      </c>
+      <c r="BE29" t="n">
+        <v>4</v>
+      </c>
+      <c r="BF29" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG29" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH29" t="n">
+        <v>0</v>
+      </c>
+      <c r="BI29" t="n">
+        <v>0</v>
+      </c>
+      <c r="BJ29" t="n">
+        <v>0</v>
+      </c>
+      <c r="BK29" t="n">
+        <v>0</v>
+      </c>
+      <c r="BL29" t="inlineStr">
+        <is>
+          <t>codex.clarity.pivot,reaction:reaction_thermalshock,reaction:reaction_deflagrate,enemy:enemy_baptism_pump_oil</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr"/>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>enemy_baptism_pump_oil</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>enemy.baptism_pump_oil.name</t>
+        </is>
+      </c>
+      <c r="D30" t="n">
+        <v>500</v>
+      </c>
+      <c r="E30" t="n">
+        <v>0</v>
+      </c>
+      <c r="F30" t="n">
+        <v>0</v>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>clarity</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>structure</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="K30" t="inlineStr">
+        <is>
+          <t>structure,acid_proof</t>
+        </is>
+      </c>
+      <c r="L30" t="n">
+        <v>0</v>
+      </c>
+      <c r="M30" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="N30" t="n">
+        <v>0</v>
+      </c>
+      <c r="O30" t="n">
+        <v>0</v>
+      </c>
+      <c r="P30" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q30" t="n">
+        <v>0</v>
+      </c>
+      <c r="R30" t="n">
+        <v>0</v>
+      </c>
+      <c r="S30" t="n">
+        <v>0</v>
+      </c>
+      <c r="T30" t="n">
+        <v>0</v>
+      </c>
+      <c r="U30" t="n">
+        <v>0</v>
+      </c>
+      <c r="V30" t="n">
+        <v>0</v>
+      </c>
+      <c r="W30" t="n">
+        <v>0</v>
+      </c>
+      <c r="X30" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y30" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA30" t="n">
+        <v>90</v>
+      </c>
+      <c r="AB30" t="inlineStr">
+        <is>
+          <t>enemy.baptism_pump_oil.desc</t>
+        </is>
+      </c>
+      <c r="AC30" t="inlineStr">
+        <is>
+          <t>enemy.baptism_pump_oil.weakness</t>
+        </is>
+      </c>
+      <c r="AD30" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="AE30" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="AF30" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="AG30" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="AH30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI30" t="inlineStr">
+        <is>
+          <t>icon_enemy_core_boss</t>
+        </is>
+      </c>
+      <c r="AJ30" t="inlineStr">
+        <is>
+          <t>clarity_tank</t>
+        </is>
+      </c>
+      <c r="AK30" t="inlineStr">
+        <is>
+          <t>#6B5A3A</t>
+        </is>
+      </c>
+      <c r="AL30" t="inlineStr">
+        <is>
+          <t>sfx_boss_phase</t>
+        </is>
+      </c>
+      <c r="AM30" t="inlineStr">
+        <is>
+          <t>vfx_boss_phase_placeholder</t>
+        </is>
+      </c>
+      <c r="AN30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ30" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA30" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB30" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC30" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD30" t="inlineStr">
+        <is>
+          <t>Oil</t>
+        </is>
+      </c>
+      <c r="BE30" t="n">
+        <v>4</v>
+      </c>
+      <c r="BF30" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG30" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH30" t="n">
+        <v>0</v>
+      </c>
+      <c r="BI30" t="n">
+        <v>0</v>
+      </c>
+      <c r="BJ30" t="n">
+        <v>0</v>
+      </c>
+      <c r="BK30" t="n">
+        <v>0</v>
+      </c>
+      <c r="BL30" t="inlineStr">
+        <is>
+          <t>enemy:enemy_baptism_tower</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr"/>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>enemy_baptism_pump_acid</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>enemy.baptism_pump_acid.name</t>
+        </is>
+      </c>
+      <c r="D31" t="n">
+        <v>500</v>
+      </c>
+      <c r="E31" t="n">
+        <v>0</v>
+      </c>
+      <c r="F31" t="n">
+        <v>0</v>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>clarity</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>structure</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="K31" t="inlineStr">
+        <is>
+          <t>structure,acid_proof</t>
+        </is>
+      </c>
+      <c r="L31" t="n">
+        <v>0</v>
+      </c>
+      <c r="M31" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="N31" t="n">
+        <v>0</v>
+      </c>
+      <c r="O31" t="n">
+        <v>0</v>
+      </c>
+      <c r="P31" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q31" t="n">
+        <v>0</v>
+      </c>
+      <c r="R31" t="n">
+        <v>0</v>
+      </c>
+      <c r="S31" t="n">
+        <v>0</v>
+      </c>
+      <c r="T31" t="n">
+        <v>0</v>
+      </c>
+      <c r="U31" t="n">
+        <v>0</v>
+      </c>
+      <c r="V31" t="n">
+        <v>0</v>
+      </c>
+      <c r="W31" t="n">
+        <v>0</v>
+      </c>
+      <c r="X31" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y31" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z31" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA31" t="n">
+        <v>90</v>
+      </c>
+      <c r="AB31" t="inlineStr">
+        <is>
+          <t>enemy.baptism_pump_acid.desc</t>
+        </is>
+      </c>
+      <c r="AC31" t="inlineStr">
+        <is>
+          <t>enemy.baptism_pump_acid.weakness</t>
+        </is>
+      </c>
+      <c r="AD31" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="AE31" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="AF31" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="AG31" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="AH31" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI31" t="inlineStr">
+        <is>
+          <t>icon_enemy_core_boss</t>
+        </is>
+      </c>
+      <c r="AJ31" t="inlineStr">
+        <is>
+          <t>clarity_tank</t>
+        </is>
+      </c>
+      <c r="AK31" t="inlineStr">
+        <is>
+          <t>#7FA83A</t>
+        </is>
+      </c>
+      <c r="AL31" t="inlineStr">
+        <is>
+          <t>sfx_boss_phase</t>
+        </is>
+      </c>
+      <c r="AM31" t="inlineStr">
+        <is>
+          <t>vfx_boss_phase_placeholder</t>
+        </is>
+      </c>
+      <c r="AN31" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO31" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP31" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ31" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR31" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS31" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT31" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU31" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV31" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW31" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX31" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY31" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ31" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA31" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB31" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC31" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD31" t="inlineStr">
+        <is>
+          <t>Acid</t>
+        </is>
+      </c>
+      <c r="BE31" t="n">
+        <v>4</v>
+      </c>
+      <c r="BF31" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG31" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH31" t="n">
+        <v>0</v>
+      </c>
+      <c r="BI31" t="n">
+        <v>0</v>
+      </c>
+      <c r="BJ31" t="n">
+        <v>0</v>
+      </c>
+      <c r="BK31" t="n">
+        <v>0</v>
+      </c>
+      <c r="BL31" t="inlineStr">
+        <is>
+          <t>enemy:enemy_baptism_tower</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr"/>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>enemy_baptism_pump_water</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>enemy.baptism_pump_water.name</t>
+        </is>
+      </c>
+      <c r="D32" t="n">
+        <v>500</v>
+      </c>
+      <c r="E32" t="n">
+        <v>0</v>
+      </c>
+      <c r="F32" t="n">
+        <v>0</v>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>clarity</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>structure</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="K32" t="inlineStr">
+        <is>
+          <t>structure,acid_proof</t>
+        </is>
+      </c>
+      <c r="L32" t="n">
+        <v>0</v>
+      </c>
+      <c r="M32" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="N32" t="n">
+        <v>0</v>
+      </c>
+      <c r="O32" t="n">
+        <v>0</v>
+      </c>
+      <c r="P32" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q32" t="n">
+        <v>0</v>
+      </c>
+      <c r="R32" t="n">
+        <v>0</v>
+      </c>
+      <c r="S32" t="n">
+        <v>0</v>
+      </c>
+      <c r="T32" t="n">
+        <v>0</v>
+      </c>
+      <c r="U32" t="n">
+        <v>0</v>
+      </c>
+      <c r="V32" t="n">
+        <v>0</v>
+      </c>
+      <c r="W32" t="n">
+        <v>0</v>
+      </c>
+      <c r="X32" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y32" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA32" t="n">
+        <v>90</v>
+      </c>
+      <c r="AB32" t="inlineStr">
+        <is>
+          <t>enemy.baptism_pump_water.desc</t>
+        </is>
+      </c>
+      <c r="AC32" t="inlineStr">
+        <is>
+          <t>enemy.baptism_pump_water.weakness</t>
+        </is>
+      </c>
+      <c r="AD32" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="AE32" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="AF32" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="AG32" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="AH32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI32" t="inlineStr">
+        <is>
+          <t>icon_enemy_core_boss</t>
+        </is>
+      </c>
+      <c r="AJ32" t="inlineStr">
+        <is>
+          <t>clarity_tank</t>
+        </is>
+      </c>
+      <c r="AK32" t="inlineStr">
+        <is>
+          <t>#3A6B9E</t>
+        </is>
+      </c>
+      <c r="AL32" t="inlineStr">
+        <is>
+          <t>sfx_boss_phase</t>
+        </is>
+      </c>
+      <c r="AM32" t="inlineStr">
+        <is>
+          <t>vfx_boss_phase_placeholder</t>
+        </is>
+      </c>
+      <c r="AN32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ32" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA32" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB32" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC32" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD32" t="inlineStr">
+        <is>
+          <t>Wet</t>
+        </is>
+      </c>
+      <c r="BE32" t="n">
+        <v>4</v>
+      </c>
+      <c r="BF32" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG32" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH32" t="n">
+        <v>0</v>
+      </c>
+      <c r="BI32" t="n">
+        <v>0</v>
+      </c>
+      <c r="BJ32" t="n">
+        <v>0</v>
+      </c>
+      <c r="BK32" t="n">
+        <v>0</v>
+      </c>
+      <c r="BL32" t="inlineStr">
+        <is>
+          <t>enemy:enemy_baptism_tower</t>
         </is>
       </c>
     </row>

--- a/Configs/GameConfig/Datas/fg/#MechEnemy-机械敌人.xlsx
+++ b/Configs/GameConfig/Datas/fg/#MechEnemy-机械敌人.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BL32"/>
+  <dimension ref="A1:BM32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -737,6 +737,11 @@
           <t>codexLinks</t>
         </is>
       </c>
+      <c r="BM1" t="inlineStr">
+        <is>
+          <t>material</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -1059,6 +1064,11 @@
           <t>string</t>
         </is>
       </c>
+      <c r="BM2" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -1379,6 +1389,11 @@
       <c r="BL3" t="inlineStr">
         <is>
           <t>FG9-UX-01 图鉴互链:逗号分隔的图鉴条目ID(reaction:/comp:/fw:/enemy:/codex.*),敌人 ↔ 弱点相关的反应 / 组件 / 机制;none=只链阵营</t>
+        </is>
+      </c>
+      <c r="BM3" t="inlineStr">
+        <is>
+          <t>材质(fg.TbEntityProfile 的 material.* 行;缺省按阵营:静默复合/铸造钢/澄净陶瓷/超频合金/舰队钢)</t>
         </is>
       </c>
     </row>
@@ -1613,6 +1628,11 @@
           <t>comp:comp_gun</t>
         </is>
       </c>
+      <c r="BM4" t="inlineStr">
+        <is>
+          <t>material.composite</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr"/>
@@ -1845,6 +1865,11 @@
           <t>comp:comp_gun,codex.signal.exposure</t>
         </is>
       </c>
+      <c r="BM5" t="inlineStr">
+        <is>
+          <t>material.composite</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr"/>
@@ -2077,6 +2102,11 @@
           <t>comp:comp_cannon</t>
         </is>
       </c>
+      <c r="BM6" t="inlineStr">
+        <is>
+          <t>material.steel</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr"/>
@@ -2309,6 +2339,11 @@
           <t>reaction:reaction_meltoverload</t>
         </is>
       </c>
+      <c r="BM7" t="inlineStr">
+        <is>
+          <t>material.steel</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr"/>
@@ -2541,6 +2576,11 @@
           <t>enemy:enemy_armorbot</t>
         </is>
       </c>
+      <c r="BM8" t="inlineStr">
+        <is>
+          <t>material.steel</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr"/>
@@ -2773,6 +2813,11 @@
           <t>enemy:enemy_core_node,codex.intel.boss_weakness</t>
         </is>
       </c>
+      <c r="BM9" t="inlineStr">
+        <is>
+          <t>material.steel</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr"/>
@@ -3005,6 +3050,11 @@
           <t>enemy:enemy_core_boss</t>
         </is>
       </c>
+      <c r="BM10" t="inlineStr">
+        <is>
+          <t>material.steel</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr"/>
@@ -3237,6 +3287,11 @@
           <t>codex.signal.exposure,codex.signal.core_firmware</t>
         </is>
       </c>
+      <c r="BM11" t="inlineStr">
+        <is>
+          <t>material.composite</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr"/>
@@ -3469,6 +3524,11 @@
           <t>comp:comp_ram</t>
         </is>
       </c>
+      <c r="BM12" t="inlineStr">
+        <is>
+          <t>material.composite</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr"/>
@@ -3701,6 +3761,11 @@
           <t>comp:func_marker,comp:struct_relay</t>
         </is>
       </c>
+      <c r="BM13" t="inlineStr">
+        <is>
+          <t>material.composite</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr"/>
@@ -3933,6 +3998,11 @@
           <t>codex.intel.listening_post</t>
         </is>
       </c>
+      <c r="BM14" t="inlineStr">
+        <is>
+          <t>material.composite</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr"/>
@@ -4165,6 +4235,11 @@
           <t>codex.signal.uplink</t>
         </is>
       </c>
+      <c r="BM15" t="inlineStr">
+        <is>
+          <t>material.composite</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr"/>
@@ -4397,6 +4472,11 @@
           <t>enemy:enemy_mind_relay,comp:func_marker,codex.intel.listening_post</t>
         </is>
       </c>
+      <c r="BM16" t="inlineStr">
+        <is>
+          <t>material.composite</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr"/>
@@ -4629,6 +4709,11 @@
           <t>enemy:enemy_mind_core,comp:func_marker</t>
         </is>
       </c>
+      <c r="BM17" t="inlineStr">
+        <is>
+          <t>material.composite</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr"/>
@@ -4861,6 +4946,11 @@
           <t>comp:comp_gun</t>
         </is>
       </c>
+      <c r="BM18" t="inlineStr">
+        <is>
+          <t>material.steel</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr"/>
@@ -5093,6 +5183,11 @@
           <t>comp:comp_gun</t>
         </is>
       </c>
+      <c r="BM19" t="inlineStr">
+        <is>
+          <t>material.steel</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr"/>
@@ -5325,6 +5420,11 @@
           <t>codex.expedition.drop</t>
         </is>
       </c>
+      <c r="BM20" t="inlineStr">
+        <is>
+          <t>material.steel</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr"/>
@@ -5557,6 +5657,11 @@
           <t>enemy:enemy_airburst,enemy:enemy_strider</t>
         </is>
       </c>
+      <c r="BM21" t="inlineStr">
+        <is>
+          <t>material.steel</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr"/>
@@ -5789,6 +5894,11 @@
           <t>reaction:reaction_meltoverload</t>
         </is>
       </c>
+      <c r="BM22" t="inlineStr">
+        <is>
+          <t>material.steel</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr"/>
@@ -6021,6 +6131,11 @@
           <t>fw:fw_coolant,codex.clarity.spray,codex.clarity.acid</t>
         </is>
       </c>
+      <c r="BM23" t="inlineStr">
+        <is>
+          <t>material.ceramic</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr"/>
@@ -6253,6 +6368,11 @@
           <t>reaction:reaction_deflagrate,fw:fw_burntrail,codex.clarity.crawler</t>
         </is>
       </c>
+      <c r="BM24" t="inlineStr">
+        <is>
+          <t>material.ceramic</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr"/>
@@ -6485,6 +6605,11 @@
           <t>codex.clarity.chill,reaction:reaction_thermalshock,fw:fw_burntrail</t>
         </is>
       </c>
+      <c r="BM25" t="inlineStr">
+        <is>
+          <t>material.ceramic</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr"/>
@@ -6717,6 +6842,11 @@
           <t>comp:comp_gun,codex.clarity.air</t>
         </is>
       </c>
+      <c r="BM26" t="inlineStr">
+        <is>
+          <t>material.ceramic</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr"/>
@@ -6949,6 +7079,11 @@
           <t>fw:fw_shockwave,fw:fw_cluster</t>
         </is>
       </c>
+      <c r="BM27" t="inlineStr">
+        <is>
+          <t>material.ceramic</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr"/>
@@ -7181,6 +7316,11 @@
           <t>codex.clarity.pivot,enemy:enemy_sprayer</t>
         </is>
       </c>
+      <c r="BM28" t="inlineStr">
+        <is>
+          <t>material.ceramic</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr"/>
@@ -7413,6 +7553,11 @@
           <t>codex.clarity.pivot,reaction:reaction_thermalshock,reaction:reaction_deflagrate,enemy:enemy_baptism_pump_oil</t>
         </is>
       </c>
+      <c r="BM29" t="inlineStr">
+        <is>
+          <t>material.ceramic</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr"/>
@@ -7645,6 +7790,11 @@
           <t>enemy:enemy_baptism_tower</t>
         </is>
       </c>
+      <c r="BM30" t="inlineStr">
+        <is>
+          <t>material.ceramic</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr"/>
@@ -7877,6 +8027,11 @@
           <t>enemy:enemy_baptism_tower</t>
         </is>
       </c>
+      <c r="BM31" t="inlineStr">
+        <is>
+          <t>material.ceramic</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr"/>
@@ -8107,6 +8262,11 @@
       <c r="BL32" t="inlineStr">
         <is>
           <t>enemy:enemy_baptism_tower</t>
+        </is>
+      </c>
+      <c r="BM32" t="inlineStr">
+        <is>
+          <t>material.ceramic</t>
         </is>
       </c>
     </row>
